--- a/research/traditional_assets/database/data/monaco/monaco_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/monaco/monaco_oil_gas_distribution.xlsx
@@ -1185,7 +1185,7 @@
         <v>0.0773856055742092</v>
       </c>
       <c r="X2">
-        <v>0.512862752180098</v>
+        <v>0.512862752180099</v>
       </c>
       <c r="Y2">
         <v>0.729459713030236</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07031265058164096</v>
+        <v>0.07017230059682755</v>
       </c>
       <c r="C2">
-        <v>3214.901045813125</v>
+        <v>3184.563787624732</v>
       </c>
       <c r="D2">
-        <v>3013.901045813125</v>
+        <v>3016.077787624732</v>
       </c>
       <c r="E2">
-        <v>-901.4</v>
+        <v>-868.886</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32.514</v>
       </c>
       <c r="G2">
         <v>201</v>
@@ -1445,28 +1445,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.6354542</v>
       </c>
       <c r="N2">
-        <v>782.7555555555555</v>
+        <v>781.1201013555554</v>
       </c>
       <c r="O2">
-        <v>193.929407936846</v>
+        <v>193.5242205670947</v>
       </c>
       <c r="P2">
-        <v>588.8261476187095</v>
+        <v>587.5958807884608</v>
       </c>
       <c r="Q2">
-        <v>779.6261476187094</v>
+        <v>778.3958807884608</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07031265058164096</v>
+        <v>0.07049890904190967</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5704136037392533</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>478.6166164454837</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07017230059682755</v>
+        <v>0.07003195061201413</v>
       </c>
       <c r="C3">
-        <v>3184.563787624732</v>
+        <v>3154.22967594275</v>
       </c>
       <c r="D3">
-        <v>3016.077787624732</v>
+        <v>3018.25767594275</v>
       </c>
       <c r="E3">
-        <v>-868.886</v>
+        <v>-836.372</v>
       </c>
       <c r="F3">
-        <v>32.514</v>
+        <v>65.02800000000001</v>
       </c>
       <c r="G3">
         <v>201</v>
@@ -1527,28 +1527,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M3">
-        <v>1.6354542</v>
+        <v>3.2709084</v>
       </c>
       <c r="N3">
-        <v>781.1201013555554</v>
+        <v>779.4846471555554</v>
       </c>
       <c r="O3">
-        <v>193.5242205670947</v>
+        <v>193.1190331973433</v>
       </c>
       <c r="P3">
-        <v>587.5958807884608</v>
+        <v>586.3656139582122</v>
       </c>
       <c r="Q3">
-        <v>778.3958807884608</v>
+        <v>777.1656139582121</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07049890904190967</v>
+        <v>0.07068896869524509</v>
       </c>
       <c r="T3">
-        <v>0.5704136037392533</v>
+        <v>0.574802972176561</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>478.6166164454837</v>
+        <v>239.3083082227419</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07003195061201413</v>
+        <v>0.06989160062720072</v>
       </c>
       <c r="C4">
-        <v>3154.22967594275</v>
+        <v>3123.898717594581</v>
       </c>
       <c r="D4">
-        <v>3018.25767594275</v>
+        <v>3020.440717594581</v>
       </c>
       <c r="E4">
-        <v>-836.372</v>
+        <v>-803.8579999999999</v>
       </c>
       <c r="F4">
-        <v>65.02800000000001</v>
+        <v>97.542</v>
       </c>
       <c r="G4">
         <v>201</v>
@@ -1609,28 +1609,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M4">
-        <v>3.2709084</v>
+        <v>4.9063626</v>
       </c>
       <c r="N4">
-        <v>779.4846471555554</v>
+        <v>777.8491929555555</v>
       </c>
       <c r="O4">
-        <v>193.1190331973433</v>
+        <v>192.7138458275919</v>
       </c>
       <c r="P4">
-        <v>586.3656139582122</v>
+        <v>585.1353471279635</v>
       </c>
       <c r="Q4">
-        <v>777.1656139582121</v>
+        <v>775.9353471279635</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07068896869524509</v>
+        <v>0.07088294710431939</v>
       </c>
       <c r="T4">
-        <v>0.574802972176561</v>
+        <v>0.5792828430558749</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>239.3083082227419</v>
+        <v>159.5388721484946</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06989160062720072</v>
+        <v>0.0697512506423873</v>
       </c>
       <c r="C5">
-        <v>3123.898717594581</v>
+        <v>3093.570919427397</v>
       </c>
       <c r="D5">
-        <v>3020.440717594581</v>
+        <v>3022.626919427397</v>
       </c>
       <c r="E5">
-        <v>-803.8579999999999</v>
+        <v>-771.3439999999999</v>
       </c>
       <c r="F5">
-        <v>97.542</v>
+        <v>130.056</v>
       </c>
       <c r="G5">
         <v>201</v>
@@ -1691,28 +1691,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M5">
-        <v>4.9063626</v>
+        <v>6.5418168</v>
       </c>
       <c r="N5">
-        <v>777.8491929555555</v>
+        <v>776.2137387555555</v>
       </c>
       <c r="O5">
-        <v>192.7138458275919</v>
+        <v>192.3086584578406</v>
       </c>
       <c r="P5">
-        <v>585.1353471279635</v>
+        <v>583.9050802977149</v>
       </c>
       <c r="Q5">
-        <v>775.9353471279635</v>
+        <v>774.7050802977149</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07088294710431939</v>
+        <v>0.07108096673024938</v>
       </c>
       <c r="T5">
-        <v>0.5792828430558749</v>
+        <v>0.5838560445785078</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>159.5388721484946</v>
+        <v>119.6541541113709</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0697512506423873</v>
+        <v>0.06961090065757389</v>
       </c>
       <c r="C6">
-        <v>3093.570919427397</v>
+        <v>3063.246288308207</v>
       </c>
       <c r="D6">
-        <v>3022.626919427397</v>
+        <v>3024.816288308207</v>
       </c>
       <c r="E6">
-        <v>-771.3439999999999</v>
+        <v>-738.8299999999999</v>
       </c>
       <c r="F6">
-        <v>130.056</v>
+        <v>162.57</v>
       </c>
       <c r="G6">
         <v>201</v>
@@ -1773,28 +1773,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M6">
-        <v>6.5418168</v>
+        <v>8.177271000000001</v>
       </c>
       <c r="N6">
-        <v>776.2137387555555</v>
+        <v>774.5782845555555</v>
       </c>
       <c r="O6">
-        <v>192.3086584578406</v>
+        <v>191.9034710880892</v>
       </c>
       <c r="P6">
-        <v>583.9050802977149</v>
+        <v>582.6748134674663</v>
       </c>
       <c r="Q6">
-        <v>774.7050802977149</v>
+        <v>773.4748134674662</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07108096673024938</v>
+        <v>0.07128315519040951</v>
       </c>
       <c r="T6">
-        <v>0.5838560445785078</v>
+        <v>0.5885255240279331</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>119.6541541113709</v>
+        <v>95.72332328909674</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06961090065757389</v>
+        <v>0.06947055067276046</v>
       </c>
       <c r="C7">
-        <v>3063.246288308207</v>
+        <v>3032.924831123929</v>
       </c>
       <c r="D7">
-        <v>3024.816288308207</v>
+        <v>3027.008831123929</v>
       </c>
       <c r="E7">
-        <v>-738.8299999999999</v>
+        <v>-706.3159999999999</v>
       </c>
       <c r="F7">
-        <v>162.57</v>
+        <v>195.084</v>
       </c>
       <c r="G7">
         <v>201</v>
@@ -1855,28 +1855,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M7">
-        <v>8.177271000000001</v>
+        <v>9.812725200000001</v>
       </c>
       <c r="N7">
-        <v>774.5782845555555</v>
+        <v>772.9428303555554</v>
       </c>
       <c r="O7">
-        <v>191.9034710880892</v>
+        <v>191.4982837183378</v>
       </c>
       <c r="P7">
-        <v>582.6748134674663</v>
+        <v>581.4445466372176</v>
       </c>
       <c r="Q7">
-        <v>773.4748134674662</v>
+        <v>772.2445466372176</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07128315519040951</v>
+        <v>0.07148964553270068</v>
       </c>
       <c r="T7">
-        <v>0.5885255240279331</v>
+        <v>0.5932943541039419</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>95.72332328909674</v>
+        <v>79.76943607424728</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06947055067276046</v>
+        <v>0.06933020068794707</v>
       </c>
       <c r="C8">
-        <v>3032.924831123929</v>
+        <v>3002.606554781465</v>
       </c>
       <c r="D8">
-        <v>3027.008831123929</v>
+        <v>3029.204554781465</v>
       </c>
       <c r="E8">
-        <v>-706.316</v>
+        <v>-673.802</v>
       </c>
       <c r="F8">
-        <v>195.084</v>
+        <v>227.598</v>
       </c>
       <c r="G8">
         <v>201</v>
@@ -1937,28 +1937,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M8">
-        <v>9.812725199999999</v>
+        <v>11.4481794</v>
       </c>
       <c r="N8">
-        <v>772.9428303555554</v>
+        <v>771.3073761555555</v>
       </c>
       <c r="O8">
-        <v>191.4982837183378</v>
+        <v>191.0930963485864</v>
       </c>
       <c r="P8">
-        <v>581.4445466372176</v>
+        <v>580.2142798069691</v>
       </c>
       <c r="Q8">
-        <v>772.2445466372176</v>
+        <v>771.0142798069692</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07148964553270068</v>
+        <v>0.07170057652751426</v>
       </c>
       <c r="T8">
-        <v>0.5932943541039419</v>
+        <v>0.5981657396654562</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>79.7694360742473</v>
+        <v>68.37380234935483</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06933020068794706</v>
+        <v>0.06918985070313365</v>
       </c>
       <c r="C9">
-        <v>3002.606554781465</v>
+        <v>2972.291466207771</v>
       </c>
       <c r="D9">
-        <v>3029.204554781465</v>
+        <v>3031.403466207771</v>
       </c>
       <c r="E9">
-        <v>-673.8019999999999</v>
+        <v>-641.288</v>
       </c>
       <c r="F9">
-        <v>227.598</v>
+        <v>260.112</v>
       </c>
       <c r="G9">
         <v>201</v>
@@ -2019,28 +2019,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M9">
-        <v>11.4481794</v>
+        <v>13.0836336</v>
       </c>
       <c r="N9">
-        <v>771.3073761555555</v>
+        <v>769.6719219555555</v>
       </c>
       <c r="O9">
-        <v>191.0930963485864</v>
+        <v>190.6879089788351</v>
       </c>
       <c r="P9">
-        <v>580.2142798069691</v>
+        <v>578.9840129767204</v>
       </c>
       <c r="Q9">
-        <v>771.0142798069692</v>
+        <v>769.7840129767203</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07170057652751426</v>
+        <v>0.07191609297873681</v>
       </c>
       <c r="T9">
-        <v>0.5981657396654562</v>
+        <v>0.6031430249130904</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>68.37380234935482</v>
+        <v>59.82707705568546</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06918985070313365</v>
+        <v>0.06904950071832022</v>
       </c>
       <c r="C10">
-        <v>2972.291466207771</v>
+        <v>2941.979572349932</v>
       </c>
       <c r="D10">
-        <v>3031.403466207771</v>
+        <v>3033.605572349932</v>
       </c>
       <c r="E10">
-        <v>-641.288</v>
+        <v>-608.774</v>
       </c>
       <c r="F10">
-        <v>260.112</v>
+        <v>292.626</v>
       </c>
       <c r="G10">
         <v>201</v>
@@ -2101,28 +2101,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M10">
-        <v>13.0836336</v>
+        <v>14.7190878</v>
       </c>
       <c r="N10">
-        <v>769.6719219555555</v>
+        <v>768.0364677555555</v>
       </c>
       <c r="O10">
-        <v>190.6879089788351</v>
+        <v>190.2827216090837</v>
       </c>
       <c r="P10">
-        <v>578.9840129767204</v>
+        <v>577.7537461464717</v>
       </c>
       <c r="Q10">
-        <v>769.7840129767203</v>
+        <v>768.5537461464717</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07191609297873681</v>
+        <v>0.07213634605526097</v>
       </c>
       <c r="T10">
-        <v>0.6031430249130904</v>
+        <v>0.608229701045288</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>59.82707705568546</v>
+        <v>53.1796240494982</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06904950071832022</v>
+        <v>0.06890915073350681</v>
       </c>
       <c r="C11">
-        <v>2941.979572349932</v>
+        <v>2911.670880175234</v>
       </c>
       <c r="D11">
-        <v>3033.605572349932</v>
+        <v>3035.810880175234</v>
       </c>
       <c r="E11">
-        <v>-608.774</v>
+        <v>-576.26</v>
       </c>
       <c r="F11">
-        <v>292.626</v>
+        <v>325.14</v>
       </c>
       <c r="G11">
         <v>201</v>
@@ -2183,28 +2183,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M11">
-        <v>14.7190878</v>
+        <v>16.354542</v>
       </c>
       <c r="N11">
-        <v>768.0364677555555</v>
+        <v>766.4010135555554</v>
       </c>
       <c r="O11">
-        <v>190.2827216090837</v>
+        <v>189.8775342393323</v>
       </c>
       <c r="P11">
-        <v>577.7537461464717</v>
+        <v>576.5234793162231</v>
       </c>
       <c r="Q11">
-        <v>768.5537461464717</v>
+        <v>767.323479316223</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07213634605526097</v>
+        <v>0.07236149364459678</v>
       </c>
       <c r="T11">
-        <v>0.608229701045288</v>
+        <v>0.6134294144248678</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>53.1796240494982</v>
+        <v>47.86166164454838</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06890915073350681</v>
+        <v>0.0687688007486934</v>
       </c>
       <c r="C12">
-        <v>2911.670880175234</v>
+        <v>2881.365396671235</v>
       </c>
       <c r="D12">
-        <v>3035.810880175234</v>
+        <v>3038.019396671235</v>
       </c>
       <c r="E12">
-        <v>-576.26</v>
+        <v>-543.746</v>
       </c>
       <c r="F12">
-        <v>325.14</v>
+        <v>357.654</v>
       </c>
       <c r="G12">
         <v>201</v>
@@ -2265,28 +2265,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M12">
-        <v>16.354542</v>
+        <v>17.9899962</v>
       </c>
       <c r="N12">
-        <v>766.4010135555554</v>
+        <v>764.7655593555555</v>
       </c>
       <c r="O12">
-        <v>189.8775342393323</v>
+        <v>189.472346869581</v>
       </c>
       <c r="P12">
-        <v>576.5234793162231</v>
+        <v>575.2932124859745</v>
       </c>
       <c r="Q12">
-        <v>767.323479316223</v>
+        <v>766.0932124859746</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07236149364459678</v>
+        <v>0.07259170073032215</v>
       </c>
       <c r="T12">
-        <v>0.6134294144248678</v>
+        <v>0.6187459752961236</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>47.86166164454837</v>
+        <v>43.51060149504398</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0687688007486934</v>
+        <v>0.06862845076387998</v>
       </c>
       <c r="C13">
-        <v>2881.365396671235</v>
+        <v>2851.063128845844</v>
       </c>
       <c r="D13">
-        <v>3038.019396671235</v>
+        <v>3040.231128845845</v>
       </c>
       <c r="E13">
-        <v>-543.746</v>
+        <v>-511.232</v>
       </c>
       <c r="F13">
-        <v>357.654</v>
+        <v>390.168</v>
       </c>
       <c r="G13">
         <v>201</v>
@@ -2347,28 +2347,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M13">
-        <v>17.9899962</v>
+        <v>19.6254504</v>
       </c>
       <c r="N13">
-        <v>764.7655593555555</v>
+        <v>763.1301051555555</v>
       </c>
       <c r="O13">
-        <v>189.472346869581</v>
+        <v>189.0671594998296</v>
       </c>
       <c r="P13">
-        <v>575.2932124859745</v>
+        <v>574.0629456557259</v>
       </c>
       <c r="Q13">
-        <v>766.0932124859746</v>
+        <v>764.862945655726</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07259170073032215</v>
+        <v>0.07282713979526856</v>
       </c>
       <c r="T13">
-        <v>0.6187459752961236</v>
+        <v>0.6241833670962714</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>43.51060149504398</v>
+        <v>39.88471803712365</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06862845076387998</v>
+        <v>0.06848810077906656</v>
       </c>
       <c r="C14">
-        <v>2851.063128845844</v>
+        <v>2820.764083727393</v>
       </c>
       <c r="D14">
-        <v>3040.231128845845</v>
+        <v>3042.446083727393</v>
       </c>
       <c r="E14">
-        <v>-511.232</v>
+        <v>-478.718</v>
       </c>
       <c r="F14">
-        <v>390.168</v>
+        <v>422.682</v>
       </c>
       <c r="G14">
         <v>201</v>
@@ -2429,28 +2429,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M14">
-        <v>19.6254504</v>
+        <v>21.2609046</v>
       </c>
       <c r="N14">
-        <v>763.1301051555555</v>
+        <v>761.4946509555555</v>
       </c>
       <c r="O14">
-        <v>189.0671594998296</v>
+        <v>188.6619721300782</v>
       </c>
       <c r="P14">
-        <v>574.0629456557259</v>
+        <v>572.8326788254773</v>
       </c>
       <c r="Q14">
-        <v>764.862945655726</v>
+        <v>763.6326788254773</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07282713979526856</v>
+        <v>0.07306799125251257</v>
       </c>
       <c r="T14">
-        <v>0.6241833670962714</v>
+        <v>0.6297457564090664</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>39.88471803712365</v>
+        <v>36.81666280349875</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06848810077906656</v>
+        <v>0.06834775079425316</v>
       </c>
       <c r="C15">
-        <v>2820.764083727393</v>
+        <v>2790.468268364706</v>
       </c>
       <c r="D15">
-        <v>3042.446083727393</v>
+        <v>3044.664268364706</v>
       </c>
       <c r="E15">
-        <v>-478.718</v>
+        <v>-446.2039999999999</v>
       </c>
       <c r="F15">
-        <v>422.682</v>
+        <v>455.1960000000001</v>
       </c>
       <c r="G15">
         <v>201</v>
@@ -2511,28 +2511,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M15">
-        <v>21.2609046</v>
+        <v>22.8963588</v>
       </c>
       <c r="N15">
-        <v>761.4946509555555</v>
+        <v>759.8591967555554</v>
       </c>
       <c r="O15">
-        <v>188.6619721300782</v>
+        <v>188.2567847603268</v>
       </c>
       <c r="P15">
-        <v>572.8326788254773</v>
+        <v>571.6024119952286</v>
       </c>
       <c r="Q15">
-        <v>763.6326788254773</v>
+        <v>762.4024119952287</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07306799125251257</v>
+        <v>0.0733144439064367</v>
       </c>
       <c r="T15">
-        <v>0.6297457564090664</v>
+        <v>0.6354375036128567</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>36.81666280349875</v>
+        <v>34.18690117467741</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06834775079425316</v>
+        <v>0.06820740080943974</v>
       </c>
       <c r="C16">
-        <v>2790.468268364706</v>
+        <v>2760.175689827185</v>
       </c>
       <c r="D16">
-        <v>3044.664268364706</v>
+        <v>3046.885689827185</v>
       </c>
       <c r="E16">
-        <v>-446.2039999999999</v>
+        <v>-413.6899999999999</v>
       </c>
       <c r="F16">
-        <v>455.1960000000001</v>
+        <v>487.7100000000001</v>
       </c>
       <c r="G16">
         <v>201</v>
@@ -2593,28 +2593,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M16">
-        <v>22.8963588</v>
+        <v>24.531813</v>
       </c>
       <c r="N16">
-        <v>759.8591967555554</v>
+        <v>758.2237425555554</v>
       </c>
       <c r="O16">
-        <v>188.2567847603268</v>
+        <v>187.8515973905754</v>
       </c>
       <c r="P16">
-        <v>571.6024119952286</v>
+        <v>570.37214516498</v>
       </c>
       <c r="Q16">
-        <v>762.4024119952287</v>
+        <v>761.1721451649801</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0733144439064367</v>
+        <v>0.0735666954463355</v>
       </c>
       <c r="T16">
-        <v>0.6354375036128567</v>
+        <v>0.6412631742802655</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>34.18690117467741</v>
+        <v>31.90777442969891</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06820740080943974</v>
+        <v>0.06806705082462633</v>
       </c>
       <c r="C17">
-        <v>2760.175689827185</v>
+        <v>2729.886355204873</v>
       </c>
       <c r="D17">
-        <v>3046.885689827185</v>
+        <v>3049.110355204873</v>
       </c>
       <c r="E17">
-        <v>-413.69</v>
+        <v>-381.1759999999999</v>
       </c>
       <c r="F17">
-        <v>487.71</v>
+        <v>520.224</v>
       </c>
       <c r="G17">
         <v>201</v>
@@ -2675,28 +2675,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M17">
-        <v>24.531813</v>
+        <v>26.1672672</v>
       </c>
       <c r="N17">
-        <v>758.2237425555555</v>
+        <v>756.5882883555555</v>
       </c>
       <c r="O17">
-        <v>187.8515973905755</v>
+        <v>187.4464100208241</v>
       </c>
       <c r="P17">
-        <v>570.3721451649801</v>
+        <v>569.1418783347314</v>
       </c>
       <c r="Q17">
-        <v>761.1721451649801</v>
+        <v>759.9418783347314</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0735666954463355</v>
+        <v>0.07382495297527951</v>
       </c>
       <c r="T17">
-        <v>0.6412631742802655</v>
+        <v>0.6472275513921364</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>31.90777442969893</v>
+        <v>29.91353852784274</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06806705082462633</v>
+        <v>0.06792670083981292</v>
       </c>
       <c r="C18">
-        <v>2729.886355204873</v>
+        <v>2699.60027160854</v>
       </c>
       <c r="D18">
-        <v>3049.110355204873</v>
+        <v>3051.338271608541</v>
       </c>
       <c r="E18">
-        <v>-381.1759999999999</v>
+        <v>-348.6619999999999</v>
       </c>
       <c r="F18">
-        <v>520.224</v>
+        <v>552.7380000000001</v>
       </c>
       <c r="G18">
         <v>201</v>
@@ -2757,28 +2757,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M18">
-        <v>26.1672672</v>
+        <v>27.8027214</v>
       </c>
       <c r="N18">
-        <v>756.5882883555555</v>
+        <v>754.9528341555555</v>
       </c>
       <c r="O18">
-        <v>187.4464100208241</v>
+        <v>187.0412226510727</v>
       </c>
       <c r="P18">
-        <v>569.1418783347314</v>
+        <v>567.9116115044827</v>
       </c>
       <c r="Q18">
-        <v>759.9418783347314</v>
+        <v>758.7116115044828</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07382495297527951</v>
+        <v>0.07408943357721012</v>
       </c>
       <c r="T18">
-        <v>0.6472275513921364</v>
+        <v>0.6533356484344138</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>29.91353852784274</v>
+        <v>28.15391861444022</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06792670083981292</v>
+        <v>0.06778635085499948</v>
       </c>
       <c r="C19">
-        <v>2699.60027160854</v>
+        <v>2669.317446169752</v>
       </c>
       <c r="D19">
-        <v>3051.338271608541</v>
+        <v>3053.569446169752</v>
       </c>
       <c r="E19">
-        <v>-348.6619999999999</v>
+        <v>-316.1479999999999</v>
       </c>
       <c r="F19">
-        <v>552.7380000000001</v>
+        <v>585.2520000000001</v>
       </c>
       <c r="G19">
         <v>201</v>
@@ -2839,28 +2839,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M19">
-        <v>27.8027214</v>
+        <v>29.4381756</v>
       </c>
       <c r="N19">
-        <v>754.9528341555555</v>
+        <v>753.3173799555555</v>
       </c>
       <c r="O19">
-        <v>187.0412226510727</v>
+        <v>186.6360352813214</v>
       </c>
       <c r="P19">
-        <v>567.9116115044827</v>
+        <v>566.6813446742341</v>
       </c>
       <c r="Q19">
-        <v>758.7116115044828</v>
+        <v>757.4813446742342</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07408943357721012</v>
+        <v>0.07436036492552928</v>
       </c>
       <c r="T19">
-        <v>0.6533356484344138</v>
+        <v>0.6595927234533322</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>28.15391861444022</v>
+        <v>26.5898120247491</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0677863508549995</v>
+        <v>0.06764600087018609</v>
       </c>
       <c r="C20">
-        <v>2669.317446169752</v>
+        <v>2639.037886040946</v>
       </c>
       <c r="D20">
-        <v>3053.569446169752</v>
+        <v>3055.803886040947</v>
       </c>
       <c r="E20">
-        <v>-316.148</v>
+        <v>-283.6339999999999</v>
       </c>
       <c r="F20">
-        <v>585.252</v>
+        <v>617.7660000000001</v>
       </c>
       <c r="G20">
         <v>201</v>
@@ -2921,28 +2921,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M20">
-        <v>29.4381756</v>
+        <v>31.0736298</v>
       </c>
       <c r="N20">
-        <v>753.3173799555555</v>
+        <v>751.6819257555554</v>
       </c>
       <c r="O20">
-        <v>186.6360352813214</v>
+        <v>186.23084791157</v>
       </c>
       <c r="P20">
-        <v>566.6813446742341</v>
+        <v>565.4510778439854</v>
       </c>
       <c r="Q20">
-        <v>757.4813446742342</v>
+        <v>756.2510778439855</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07436036492552928</v>
+        <v>0.0746379859367699</v>
       </c>
       <c r="T20">
-        <v>0.6595927234533322</v>
+        <v>0.66600429415173</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>26.5898120247491</v>
+        <v>25.19034823397283</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06764600087018609</v>
+        <v>0.06750565088537268</v>
       </c>
       <c r="C21">
-        <v>2639.037886040946</v>
+        <v>2608.761598395515</v>
       </c>
       <c r="D21">
-        <v>3055.803886040947</v>
+        <v>3058.041598395515</v>
       </c>
       <c r="E21">
-        <v>-283.6339999999999</v>
+        <v>-251.1199999999999</v>
       </c>
       <c r="F21">
-        <v>617.7660000000001</v>
+        <v>650.2800000000001</v>
       </c>
       <c r="G21">
         <v>201</v>
@@ -3003,28 +3003,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M21">
-        <v>31.0736298</v>
+        <v>32.709084</v>
       </c>
       <c r="N21">
-        <v>751.6819257555554</v>
+        <v>750.0464715555555</v>
       </c>
       <c r="O21">
-        <v>186.23084791157</v>
+        <v>185.8256605418186</v>
       </c>
       <c r="P21">
-        <v>565.4510778439854</v>
+        <v>564.2208110137369</v>
       </c>
       <c r="Q21">
-        <v>756.2510778439855</v>
+        <v>755.0208110137369</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0746379859367699</v>
+        <v>0.07492254747329155</v>
       </c>
       <c r="T21">
-        <v>0.66600429415173</v>
+        <v>0.6725761541175878</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>25.19034823397283</v>
+        <v>23.93083082227419</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06750565088537268</v>
+        <v>0.06736530090055926</v>
       </c>
       <c r="C22">
-        <v>2608.761598395515</v>
+        <v>2578.488590427874</v>
       </c>
       <c r="D22">
-        <v>3058.041598395515</v>
+        <v>3060.282590427874</v>
       </c>
       <c r="E22">
-        <v>-251.1199999999999</v>
+        <v>-218.6059999999999</v>
       </c>
       <c r="F22">
-        <v>650.2800000000001</v>
+        <v>682.7940000000001</v>
       </c>
       <c r="G22">
         <v>201</v>
@@ -3085,28 +3085,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M22">
-        <v>32.709084</v>
+        <v>34.3445382</v>
       </c>
       <c r="N22">
-        <v>750.0464715555555</v>
+        <v>748.4110173555555</v>
       </c>
       <c r="O22">
-        <v>185.8256605418186</v>
+        <v>185.4204731720673</v>
       </c>
       <c r="P22">
-        <v>564.2208110137369</v>
+        <v>562.9905441834883</v>
       </c>
       <c r="Q22">
-        <v>755.0208110137369</v>
+        <v>753.7905441834882</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07492254747329155</v>
+        <v>0.07521431309934538</v>
       </c>
       <c r="T22">
-        <v>0.6725761541175878</v>
+        <v>0.6793143902851129</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>23.93083082227419</v>
+        <v>22.79126744978494</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06736530090055926</v>
+        <v>0.06722495091574585</v>
       </c>
       <c r="C23">
-        <v>2578.488590427874</v>
+        <v>2548.218869353547</v>
       </c>
       <c r="D23">
-        <v>3060.282590427874</v>
+        <v>3062.526869353547</v>
       </c>
       <c r="E23">
-        <v>-218.606</v>
+        <v>-186.092</v>
       </c>
       <c r="F23">
-        <v>682.794</v>
+        <v>715.308</v>
       </c>
       <c r="G23">
         <v>201</v>
@@ -3167,28 +3167,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M23">
-        <v>34.3445382</v>
+        <v>35.9799924</v>
       </c>
       <c r="N23">
-        <v>748.4110173555555</v>
+        <v>746.7755631555555</v>
       </c>
       <c r="O23">
-        <v>185.4204731720673</v>
+        <v>185.0152858023159</v>
       </c>
       <c r="P23">
-        <v>562.9905441834883</v>
+        <v>561.7602773532396</v>
       </c>
       <c r="Q23">
-        <v>753.7905441834882</v>
+        <v>752.5602773532396</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07521431309934538</v>
+        <v>0.07551355989529804</v>
       </c>
       <c r="T23">
-        <v>0.6793143902851129</v>
+        <v>0.6862254017389847</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>22.79126744978494</v>
+        <v>21.75530074752199</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06722495091574585</v>
+        <v>0.06708460093093244</v>
       </c>
       <c r="C24">
-        <v>2548.218869353547</v>
+        <v>2517.952442409236</v>
       </c>
       <c r="D24">
-        <v>3062.526869353547</v>
+        <v>3064.774442409236</v>
       </c>
       <c r="E24">
-        <v>-186.092</v>
+        <v>-153.578</v>
       </c>
       <c r="F24">
-        <v>715.308</v>
+        <v>747.822</v>
       </c>
       <c r="G24">
         <v>201</v>
@@ -3249,28 +3249,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M24">
-        <v>35.9799924</v>
+        <v>37.6154466</v>
       </c>
       <c r="N24">
-        <v>746.7755631555555</v>
+        <v>745.1401089555554</v>
       </c>
       <c r="O24">
-        <v>185.0152858023159</v>
+        <v>184.6100984325645</v>
       </c>
       <c r="P24">
-        <v>561.7602773532396</v>
+        <v>560.5300105229909</v>
       </c>
       <c r="Q24">
-        <v>752.5602773532396</v>
+        <v>751.330010522991</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07551355989529804</v>
+        <v>0.07582057933530141</v>
       </c>
       <c r="T24">
-        <v>0.6862254017389847</v>
+        <v>0.6933159199838662</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>21.75530074752199</v>
+        <v>20.80941810632538</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06708460093093244</v>
+        <v>0.06694425094611903</v>
       </c>
       <c r="C25">
-        <v>2517.952442409236</v>
+        <v>2487.689316852903</v>
       </c>
       <c r="D25">
-        <v>3064.774442409236</v>
+        <v>3067.025316852903</v>
       </c>
       <c r="E25">
-        <v>-153.578</v>
+        <v>-121.0639999999999</v>
       </c>
       <c r="F25">
-        <v>747.822</v>
+        <v>780.3360000000001</v>
       </c>
       <c r="G25">
         <v>201</v>
@@ -3331,28 +3331,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M25">
-        <v>37.6154466</v>
+        <v>39.2509008</v>
       </c>
       <c r="N25">
-        <v>745.1401089555554</v>
+        <v>743.5046547555555</v>
       </c>
       <c r="O25">
-        <v>184.6100984325645</v>
+        <v>184.2049110628132</v>
       </c>
       <c r="P25">
-        <v>560.5300105229909</v>
+        <v>559.2997436927424</v>
       </c>
       <c r="Q25">
-        <v>751.330010522991</v>
+        <v>750.0997436927423</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07582057933530141</v>
+        <v>0.07613567823425224</v>
       </c>
       <c r="T25">
-        <v>0.6933159199838662</v>
+        <v>0.7005930308141394</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>20.80941810632538</v>
+        <v>19.94235901856182</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06694425094611903</v>
+        <v>0.06680390096130559</v>
       </c>
       <c r="C26">
-        <v>2487.689316852903</v>
+        <v>2457.429499963851</v>
       </c>
       <c r="D26">
-        <v>3067.025316852903</v>
+        <v>3069.279499963851</v>
       </c>
       <c r="E26">
-        <v>-121.064</v>
+        <v>-88.54999999999995</v>
       </c>
       <c r="F26">
-        <v>780.336</v>
+        <v>812.85</v>
       </c>
       <c r="G26">
         <v>201</v>
@@ -3413,28 +3413,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M26">
-        <v>39.2509008</v>
+        <v>40.886355</v>
       </c>
       <c r="N26">
-        <v>743.5046547555555</v>
+        <v>741.8692005555555</v>
       </c>
       <c r="O26">
-        <v>184.2049110628132</v>
+        <v>183.7997236930618</v>
       </c>
       <c r="P26">
-        <v>559.2997436927424</v>
+        <v>558.0694768624937</v>
       </c>
       <c r="Q26">
-        <v>750.0997436927423</v>
+        <v>748.8694768624937</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07613567823425224</v>
+        <v>0.07645917977050841</v>
       </c>
       <c r="T26">
-        <v>0.7005930308141394</v>
+        <v>0.7080641979332197</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>19.94235901856183</v>
+        <v>19.14466465781935</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06680390096130559</v>
+        <v>0.06666355097649218</v>
       </c>
       <c r="C27">
-        <v>2457.429499963851</v>
+        <v>2427.172999042794</v>
       </c>
       <c r="D27">
-        <v>3069.279499963851</v>
+        <v>3071.536999042794</v>
       </c>
       <c r="E27">
-        <v>-88.54999999999995</v>
+        <v>-56.03599999999994</v>
       </c>
       <c r="F27">
-        <v>812.85</v>
+        <v>845.364</v>
       </c>
       <c r="G27">
         <v>201</v>
@@ -3495,28 +3495,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M27">
-        <v>40.886355</v>
+        <v>42.5218092</v>
       </c>
       <c r="N27">
-        <v>741.8692005555555</v>
+        <v>740.2337463555555</v>
       </c>
       <c r="O27">
-        <v>183.7997236930618</v>
+        <v>183.3945363233104</v>
       </c>
       <c r="P27">
-        <v>558.0694768624937</v>
+        <v>556.8392100322451</v>
       </c>
       <c r="Q27">
-        <v>748.8694768624937</v>
+        <v>747.639210032245</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07645917977050841</v>
+        <v>0.07679142459152828</v>
       </c>
       <c r="T27">
-        <v>0.7080641979332197</v>
+        <v>0.715737288487951</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.14466465781935</v>
+        <v>18.40833140174938</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06666355097649218</v>
+        <v>0.06652320099167877</v>
       </c>
       <c r="C28">
-        <v>2427.172999042794</v>
+        <v>2396.919821411946</v>
       </c>
       <c r="D28">
-        <v>3071.536999042794</v>
+        <v>3073.797821411946</v>
       </c>
       <c r="E28">
-        <v>-56.03599999999994</v>
+        <v>-23.52199999999993</v>
       </c>
       <c r="F28">
-        <v>845.364</v>
+        <v>877.878</v>
       </c>
       <c r="G28">
         <v>201</v>
@@ -3577,28 +3577,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M28">
-        <v>42.5218092</v>
+        <v>44.1572634</v>
       </c>
       <c r="N28">
-        <v>740.2337463555555</v>
+        <v>738.5982921555554</v>
       </c>
       <c r="O28">
-        <v>183.3945363233104</v>
+        <v>182.989348953559</v>
       </c>
       <c r="P28">
-        <v>556.8392100322451</v>
+        <v>555.6089432019965</v>
       </c>
       <c r="Q28">
-        <v>747.639210032245</v>
+        <v>746.4089432019964</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07679142459152828</v>
+        <v>0.07713277201038429</v>
       </c>
       <c r="T28">
-        <v>0.715737288487951</v>
+        <v>0.723620600701716</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>18.40833140174938</v>
+        <v>17.72654134983273</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06652320099167877</v>
+        <v>0.06638285100686536</v>
       </c>
       <c r="C29">
-        <v>2396.919821411946</v>
+        <v>2366.66997441509</v>
       </c>
       <c r="D29">
-        <v>3073.797821411946</v>
+        <v>3076.06197441509</v>
       </c>
       <c r="E29">
-        <v>-23.52199999999993</v>
+        <v>8.992000000000189</v>
       </c>
       <c r="F29">
-        <v>877.878</v>
+        <v>910.3920000000002</v>
       </c>
       <c r="G29">
         <v>201</v>
@@ -3659,28 +3659,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M29">
-        <v>44.1572634</v>
+        <v>45.7927176</v>
       </c>
       <c r="N29">
-        <v>738.5982921555554</v>
+        <v>736.9628379555554</v>
       </c>
       <c r="O29">
-        <v>182.989348953559</v>
+        <v>182.5841615838077</v>
       </c>
       <c r="P29">
-        <v>555.6089432019965</v>
+        <v>554.3786763717478</v>
       </c>
       <c r="Q29">
-        <v>746.4089432019964</v>
+        <v>745.1786763717478</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07713277201038429</v>
+        <v>0.07748360130198632</v>
       </c>
       <c r="T29">
-        <v>0.723620600701716</v>
+        <v>0.7317228938103078</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>17.72654134983273</v>
+        <v>17.0934505873387</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06638285100686536</v>
+        <v>0.06624250102205194</v>
       </c>
       <c r="C30">
-        <v>2366.66997441509</v>
+        <v>2336.423465417668</v>
       </c>
       <c r="D30">
-        <v>3076.06197441509</v>
+        <v>3078.329465417668</v>
       </c>
       <c r="E30">
-        <v>8.992000000000189</v>
+        <v>41.5060000000002</v>
       </c>
       <c r="F30">
-        <v>910.3920000000002</v>
+        <v>942.9060000000002</v>
       </c>
       <c r="G30">
         <v>201</v>
@@ -3741,28 +3741,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M30">
-        <v>45.7927176</v>
+        <v>47.42817180000001</v>
       </c>
       <c r="N30">
-        <v>736.9628379555554</v>
+        <v>735.3273837555555</v>
       </c>
       <c r="O30">
-        <v>182.5841615838077</v>
+        <v>182.1789742140563</v>
       </c>
       <c r="P30">
-        <v>554.3786763717478</v>
+        <v>553.1484095414992</v>
       </c>
       <c r="Q30">
-        <v>745.1786763717478</v>
+        <v>743.9484095414991</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07748360130198632</v>
+        <v>0.07784431310884474</v>
       </c>
       <c r="T30">
-        <v>0.7317228938103078</v>
+        <v>0.7400534205275923</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.0934505873387</v>
+        <v>16.50402125674082</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06624250102205194</v>
+        <v>0.06610215103723853</v>
       </c>
       <c r="C31">
-        <v>2336.423465417668</v>
+        <v>2306.180301806852</v>
       </c>
       <c r="D31">
-        <v>3078.329465417668</v>
+        <v>3080.600301806852</v>
       </c>
       <c r="E31">
-        <v>41.50599999999997</v>
+        <v>74.01999999999998</v>
       </c>
       <c r="F31">
-        <v>942.9059999999999</v>
+        <v>975.42</v>
       </c>
       <c r="G31">
         <v>201</v>
@@ -3823,28 +3823,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M31">
-        <v>47.42817179999999</v>
+        <v>49.06362599999999</v>
       </c>
       <c r="N31">
-        <v>735.3273837555555</v>
+        <v>733.6919295555555</v>
       </c>
       <c r="O31">
-        <v>182.1789742140563</v>
+        <v>181.7737868443049</v>
       </c>
       <c r="P31">
-        <v>553.1484095414992</v>
+        <v>551.9181427112505</v>
       </c>
       <c r="Q31">
-        <v>743.9484095414991</v>
+        <v>742.7181427112505</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07784431310884474</v>
+        <v>0.07821533096732769</v>
       </c>
       <c r="T31">
-        <v>0.7400534205275923</v>
+        <v>0.7486219622939421</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>16.50402125674082</v>
+        <v>15.95388721484946</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06610215103723853</v>
+        <v>0.06596180105242511</v>
       </c>
       <c r="C32">
-        <v>2306.180301806852</v>
+        <v>2275.940490991627</v>
       </c>
       <c r="D32">
-        <v>3080.600301806852</v>
+        <v>3082.874490991628</v>
       </c>
       <c r="E32">
-        <v>74.01999999999998</v>
+        <v>106.534</v>
       </c>
       <c r="F32">
-        <v>975.42</v>
+        <v>1007.934</v>
       </c>
       <c r="G32">
         <v>201</v>
@@ -3905,28 +3905,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M32">
-        <v>49.06362599999999</v>
+        <v>50.6990802</v>
       </c>
       <c r="N32">
-        <v>733.6919295555555</v>
+        <v>732.0564753555554</v>
       </c>
       <c r="O32">
-        <v>181.7737868443049</v>
+        <v>181.3685994745535</v>
       </c>
       <c r="P32">
-        <v>551.9181427112505</v>
+        <v>550.6878758810019</v>
       </c>
       <c r="Q32">
-        <v>742.7181427112505</v>
+        <v>741.4878758810019</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07821533096732769</v>
+        <v>0.07859710296663622</v>
       </c>
       <c r="T32">
-        <v>0.7486219622939421</v>
+        <v>0.7574388675897512</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>15.95388721484946</v>
+        <v>15.4392456917898</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06596180105242511</v>
+        <v>0.0658214510676117</v>
       </c>
       <c r="C33">
-        <v>2275.940490991627</v>
+        <v>2245.704040402877</v>
       </c>
       <c r="D33">
-        <v>3082.874490991628</v>
+        <v>3085.152040402877</v>
       </c>
       <c r="E33">
-        <v>106.534</v>
+        <v>139.0480000000001</v>
       </c>
       <c r="F33">
-        <v>1007.934</v>
+        <v>1040.448</v>
       </c>
       <c r="G33">
         <v>201</v>
@@ -3987,28 +3987,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M33">
-        <v>50.6990802</v>
+        <v>52.3345344</v>
       </c>
       <c r="N33">
-        <v>732.0564753555554</v>
+        <v>730.4210211555554</v>
       </c>
       <c r="O33">
-        <v>181.3685994745535</v>
+        <v>180.9634121048022</v>
       </c>
       <c r="P33">
-        <v>550.6878758810019</v>
+        <v>549.4576090507533</v>
       </c>
       <c r="Q33">
-        <v>741.4878758810019</v>
+        <v>740.2576090507532</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07859710296663622</v>
+        <v>0.07899010355415972</v>
       </c>
       <c r="T33">
-        <v>0.7574388675897512</v>
+        <v>0.7665150936295549</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.4392456917898</v>
+        <v>14.95676926392137</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0658214510676117</v>
+        <v>0.06568110108279829</v>
       </c>
       <c r="C34">
-        <v>2245.704040402877</v>
+        <v>2215.470957493455</v>
       </c>
       <c r="D34">
-        <v>3085.152040402877</v>
+        <v>3087.432957493455</v>
       </c>
       <c r="E34">
-        <v>139.0480000000001</v>
+        <v>171.562</v>
       </c>
       <c r="F34">
-        <v>1040.448</v>
+        <v>1072.962</v>
       </c>
       <c r="G34">
         <v>201</v>
@@ -4069,28 +4069,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M34">
-        <v>52.3345344</v>
+        <v>53.96998859999999</v>
       </c>
       <c r="N34">
-        <v>730.4210211555554</v>
+        <v>728.7855669555555</v>
       </c>
       <c r="O34">
-        <v>180.9634121048022</v>
+        <v>180.5582247350508</v>
       </c>
       <c r="P34">
-        <v>549.4576090507533</v>
+        <v>548.2273422205046</v>
       </c>
       <c r="Q34">
-        <v>740.2576090507532</v>
+        <v>739.0273422205046</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07899010355415972</v>
+        <v>0.07939483550250481</v>
       </c>
       <c r="T34">
-        <v>0.7665150936295549</v>
+        <v>0.7758622517899496</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>14.95676926392137</v>
+        <v>14.50353383168133</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06568110108279829</v>
+        <v>0.06554075109798488</v>
       </c>
       <c r="C35">
-        <v>2215.470957493455</v>
+        <v>2185.241249738274</v>
       </c>
       <c r="D35">
-        <v>3087.432957493455</v>
+        <v>3089.717249738274</v>
       </c>
       <c r="E35">
-        <v>171.562</v>
+        <v>204.0760000000001</v>
       </c>
       <c r="F35">
-        <v>1072.962</v>
+        <v>1105.476</v>
       </c>
       <c r="G35">
         <v>201</v>
@@ -4151,28 +4151,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M35">
-        <v>53.96998859999999</v>
+        <v>55.60544280000001</v>
       </c>
       <c r="N35">
-        <v>728.7855669555555</v>
+        <v>727.1501127555555</v>
       </c>
       <c r="O35">
-        <v>180.5582247350508</v>
+        <v>180.1530373652994</v>
       </c>
       <c r="P35">
-        <v>548.2273422205046</v>
+        <v>546.997075390256</v>
       </c>
       <c r="Q35">
-        <v>739.0273422205046</v>
+        <v>737.7970753902559</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07939483550250481</v>
+        <v>0.07981183205534523</v>
       </c>
       <c r="T35">
-        <v>0.7758622517899496</v>
+        <v>0.7854926571673261</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.50353383168133</v>
+        <v>14.07695930722011</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06554075109798488</v>
+        <v>0.06540040111317146</v>
       </c>
       <c r="C36">
-        <v>2185.241249738274</v>
+        <v>2155.014924634385</v>
       </c>
       <c r="D36">
-        <v>3089.717249738274</v>
+        <v>3092.004924634386</v>
       </c>
       <c r="E36">
-        <v>204.0760000000001</v>
+        <v>236.5900000000003</v>
       </c>
       <c r="F36">
-        <v>1105.476</v>
+        <v>1137.99</v>
       </c>
       <c r="G36">
         <v>201</v>
@@ -4233,28 +4233,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M36">
-        <v>55.60544280000001</v>
+        <v>57.24089700000001</v>
       </c>
       <c r="N36">
-        <v>727.1501127555555</v>
+        <v>725.5146585555555</v>
       </c>
       <c r="O36">
-        <v>180.1530373652994</v>
+        <v>179.7478499955481</v>
       </c>
       <c r="P36">
-        <v>546.997075390256</v>
+        <v>545.7668085600073</v>
       </c>
       <c r="Q36">
-        <v>737.7970753902559</v>
+        <v>736.5668085600073</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07981183205534523</v>
+        <v>0.08024165927134994</v>
       </c>
       <c r="T36">
-        <v>0.7854926571673261</v>
+        <v>0.7954193827101601</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.07695930722011</v>
+        <v>13.67476046987096</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06540040111317146</v>
+        <v>0.06526005112835805</v>
       </c>
       <c r="C37">
-        <v>2155.014924634385</v>
+        <v>2124.791989701061</v>
       </c>
       <c r="D37">
-        <v>3092.004924634386</v>
+        <v>3094.295989701061</v>
       </c>
       <c r="E37">
-        <v>236.5900000000003</v>
+        <v>269.1040000000002</v>
       </c>
       <c r="F37">
-        <v>1137.99</v>
+        <v>1170.504</v>
       </c>
       <c r="G37">
         <v>201</v>
@@ -4315,28 +4315,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M37">
-        <v>57.24089700000001</v>
+        <v>58.8763512</v>
       </c>
       <c r="N37">
-        <v>725.5146585555555</v>
+        <v>723.8792043555554</v>
       </c>
       <c r="O37">
-        <v>179.7478499955481</v>
+        <v>179.3426626257967</v>
       </c>
       <c r="P37">
-        <v>545.7668085600073</v>
+        <v>544.5365417297587</v>
       </c>
       <c r="Q37">
-        <v>736.5668085600073</v>
+        <v>735.3365417297587</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08024165927134994</v>
+        <v>0.0806849185878548</v>
       </c>
       <c r="T37">
-        <v>0.7954193827101601</v>
+        <v>0.8056563184262079</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>13.67476046987096</v>
+        <v>13.29490601237455</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06526005112835805</v>
+        <v>0.06511970114354464</v>
       </c>
       <c r="C38">
-        <v>2124.791989701061</v>
+        <v>2094.572452479872</v>
       </c>
       <c r="D38">
-        <v>3094.295989701061</v>
+        <v>3096.590452479873</v>
       </c>
       <c r="E38">
-        <v>269.1039999999999</v>
+        <v>301.6180000000001</v>
       </c>
       <c r="F38">
-        <v>1170.504</v>
+        <v>1203.018</v>
       </c>
       <c r="G38">
         <v>201</v>
@@ -4397,28 +4397,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M38">
-        <v>58.87635119999999</v>
+        <v>60.5118054</v>
       </c>
       <c r="N38">
-        <v>723.8792043555554</v>
+        <v>722.2437501555555</v>
       </c>
       <c r="O38">
-        <v>179.3426626257967</v>
+        <v>178.9374752560453</v>
       </c>
       <c r="P38">
-        <v>544.5365417297587</v>
+        <v>543.3062748995102</v>
       </c>
       <c r="Q38">
-        <v>735.3365417297587</v>
+        <v>734.1062748995103</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08068491858785479</v>
+        <v>0.08114224962869315</v>
       </c>
       <c r="T38">
-        <v>0.8056563184262077</v>
+        <v>0.8162182362284791</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.29490601237455</v>
+        <v>12.93558422825632</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06511970114354464</v>
+        <v>0.06540813240692619</v>
       </c>
       <c r="C39">
-        <v>2094.572452479872</v>
+        <v>2057.346818028256</v>
       </c>
       <c r="D39">
-        <v>3096.590452479873</v>
+        <v>3091.878818028256</v>
       </c>
       <c r="E39">
-        <v>301.6180000000001</v>
+        <v>334.1320000000002</v>
       </c>
       <c r="F39">
-        <v>1203.018</v>
+        <v>1235.532</v>
       </c>
       <c r="G39">
         <v>201</v>
@@ -4479,45 +4479,45 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M39">
-        <v>60.5118054</v>
+        <v>64.00055760000001</v>
       </c>
       <c r="N39">
-        <v>722.2437501555555</v>
+        <v>718.7549979555555</v>
       </c>
       <c r="O39">
-        <v>178.9374752560453</v>
+        <v>178.0731292366751</v>
       </c>
       <c r="P39">
-        <v>543.3062748995102</v>
+        <v>540.6818687188804</v>
       </c>
       <c r="Q39">
-        <v>734.1062748995103</v>
+        <v>731.4818687188804</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08114224962869315</v>
+        <v>0.08161433328375209</v>
       </c>
       <c r="T39">
-        <v>0.8162182362284791</v>
+        <v>0.8271208610566304</v>
       </c>
       <c r="U39">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V39">
         <v>0.2477521961491617</v>
       </c>
       <c r="W39">
-        <v>0.03783806453369716</v>
+        <v>0.03896643623947342</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y39">
-        <v>12.93558422825632</v>
+        <v>12.23044899776866</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06540813240692619</v>
+        <v>0.06527906613917055</v>
       </c>
       <c r="C40">
-        <v>2057.346818028256</v>
+        <v>2026.939390945101</v>
       </c>
       <c r="D40">
-        <v>3091.878818028256</v>
+        <v>3093.985390945101</v>
       </c>
       <c r="E40">
-        <v>334.1320000000002</v>
+        <v>366.6460000000001</v>
       </c>
       <c r="F40">
-        <v>1235.532</v>
+        <v>1268.046</v>
       </c>
       <c r="G40">
         <v>201</v>
@@ -4561,28 +4561,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M40">
-        <v>64.00055760000001</v>
+        <v>65.68478280000001</v>
       </c>
       <c r="N40">
-        <v>718.7549979555555</v>
+        <v>717.0707727555555</v>
       </c>
       <c r="O40">
-        <v>178.0731292366751</v>
+        <v>177.6558587445654</v>
       </c>
       <c r="P40">
-        <v>540.6818687188804</v>
+        <v>539.4149140109901</v>
       </c>
       <c r="Q40">
-        <v>731.4818687188804</v>
+        <v>730.21491401099</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08161433328375209</v>
+        <v>0.08210189509143592</v>
       </c>
       <c r="T40">
-        <v>0.8271208610566304</v>
+        <v>0.8383809489939013</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>12.23044899776866</v>
+        <v>11.91684774141562</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06527906613917055</v>
+        <v>0.0651499998714149</v>
       </c>
       <c r="C41">
-        <v>2026.939390945101</v>
+        <v>1996.534836338685</v>
       </c>
       <c r="D41">
-        <v>3093.985390945101</v>
+        <v>3096.094836338686</v>
       </c>
       <c r="E41">
-        <v>366.6460000000001</v>
+        <v>399.1600000000002</v>
       </c>
       <c r="F41">
-        <v>1268.046</v>
+        <v>1300.56</v>
       </c>
       <c r="G41">
         <v>201</v>
@@ -4643,28 +4643,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M41">
-        <v>65.68478280000001</v>
+        <v>67.36900800000001</v>
       </c>
       <c r="N41">
-        <v>717.0707727555555</v>
+        <v>715.3865475555555</v>
       </c>
       <c r="O41">
-        <v>177.6558587445654</v>
+        <v>177.2385882524556</v>
       </c>
       <c r="P41">
-        <v>539.4149140109901</v>
+        <v>538.1479593030999</v>
       </c>
       <c r="Q41">
-        <v>730.21491401099</v>
+        <v>728.9479593030999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08210189509143592</v>
+        <v>0.08260570895937588</v>
       </c>
       <c r="T41">
-        <v>0.8383809489939013</v>
+        <v>0.8500163731957477</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.91684774141562</v>
+        <v>11.61892654788023</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0651499998714149</v>
+        <v>0.06502093360365924</v>
       </c>
       <c r="C42">
-        <v>1996.534836338685</v>
+        <v>1966.13316008829</v>
       </c>
       <c r="D42">
-        <v>3096.094836338686</v>
+        <v>3098.20716008829</v>
       </c>
       <c r="E42">
-        <v>399.1600000000002</v>
+        <v>431.6740000000001</v>
       </c>
       <c r="F42">
-        <v>1300.56</v>
+        <v>1333.074</v>
       </c>
       <c r="G42">
         <v>201</v>
@@ -4725,28 +4725,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M42">
-        <v>67.36900800000001</v>
+        <v>69.05323320000001</v>
       </c>
       <c r="N42">
-        <v>715.3865475555555</v>
+        <v>713.7023223555555</v>
       </c>
       <c r="O42">
-        <v>177.2385882524556</v>
+        <v>176.8213177603458</v>
       </c>
       <c r="P42">
-        <v>538.1479593030999</v>
+        <v>536.8810045952096</v>
       </c>
       <c r="Q42">
-        <v>728.9479593030999</v>
+        <v>727.6810045952095</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08260570895937588</v>
+        <v>0.08312660126351719</v>
       </c>
       <c r="T42">
-        <v>0.8500163731957477</v>
+        <v>0.862046218556979</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.61892654788023</v>
+        <v>11.3355380954929</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06502093360365924</v>
+        <v>0.06489186733590359</v>
       </c>
       <c r="C43">
-        <v>1966.13316008829</v>
+        <v>1935.734368089246</v>
       </c>
       <c r="D43">
-        <v>3098.20716008829</v>
+        <v>3100.322368089247</v>
       </c>
       <c r="E43">
-        <v>431.6740000000001</v>
+        <v>464.1880000000002</v>
       </c>
       <c r="F43">
-        <v>1333.074</v>
+        <v>1365.588</v>
       </c>
       <c r="G43">
         <v>201</v>
@@ -4807,28 +4807,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M43">
-        <v>69.05323320000001</v>
+        <v>70.73745840000001</v>
       </c>
       <c r="N43">
-        <v>713.7023223555555</v>
+        <v>712.0180971555554</v>
       </c>
       <c r="O43">
-        <v>176.8213177603458</v>
+        <v>176.4040472682361</v>
       </c>
       <c r="P43">
-        <v>536.8810045952096</v>
+        <v>535.6140498873194</v>
       </c>
       <c r="Q43">
-        <v>727.6810045952095</v>
+        <v>726.4140498873194</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08312660126351719</v>
+        <v>0.08366545537124959</v>
       </c>
       <c r="T43">
-        <v>0.862046218556979</v>
+        <v>0.8744908861720457</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.3355380954929</v>
+        <v>11.0656443313145</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06489186733590359</v>
+        <v>0.06476280106814794</v>
       </c>
       <c r="C44">
-        <v>1935.734368089247</v>
+        <v>1905.338466252999</v>
       </c>
       <c r="D44">
-        <v>3100.322368089247</v>
+        <v>3102.440466252999</v>
       </c>
       <c r="E44">
-        <v>464.188</v>
+        <v>496.7020000000001</v>
       </c>
       <c r="F44">
-        <v>1365.588</v>
+        <v>1398.102</v>
       </c>
       <c r="G44">
         <v>201</v>
@@ -4889,28 +4889,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M44">
-        <v>70.73745839999999</v>
+        <v>72.42168360000001</v>
       </c>
       <c r="N44">
-        <v>712.0180971555554</v>
+        <v>710.3338719555554</v>
       </c>
       <c r="O44">
-        <v>176.4040472682361</v>
+        <v>175.9867767761263</v>
       </c>
       <c r="P44">
-        <v>535.6140498873194</v>
+        <v>534.3470951794291</v>
       </c>
       <c r="Q44">
-        <v>726.4140498873194</v>
+        <v>725.147095179429</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08366545537124957</v>
+        <v>0.08422321664065678</v>
       </c>
       <c r="T44">
-        <v>0.8744908861720455</v>
+        <v>0.8873722087911498</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.0656443313145</v>
+        <v>10.80830376546998</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06476280106814794</v>
+        <v>0.06463373480039229</v>
       </c>
       <c r="C45">
-        <v>1905.338466252999</v>
+        <v>1874.945460507158</v>
       </c>
       <c r="D45">
-        <v>3102.440466252999</v>
+        <v>3104.561460507158</v>
       </c>
       <c r="E45">
-        <v>496.7020000000001</v>
+        <v>529.216</v>
       </c>
       <c r="F45">
-        <v>1398.102</v>
+        <v>1430.616</v>
       </c>
       <c r="G45">
         <v>201</v>
@@ -4971,28 +4971,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M45">
-        <v>72.42168360000001</v>
+        <v>74.10590879999999</v>
       </c>
       <c r="N45">
-        <v>710.3338719555554</v>
+        <v>708.6496467555555</v>
       </c>
       <c r="O45">
-        <v>175.9867767761263</v>
+        <v>175.5695062840166</v>
       </c>
       <c r="P45">
-        <v>534.3470951794291</v>
+        <v>533.0801404715389</v>
       </c>
       <c r="Q45">
-        <v>725.147095179429</v>
+        <v>723.8801404715389</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08422321664065678</v>
+        <v>0.08480089795539997</v>
       </c>
       <c r="T45">
-        <v>0.8873722087911498</v>
+        <v>0.9007135786466505</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.80830376546998</v>
+        <v>10.56266049807294</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06463373480039229</v>
+        <v>0.06450466853263664</v>
       </c>
       <c r="C46">
-        <v>1874.945460507158</v>
+        <v>1844.555356795554</v>
       </c>
       <c r="D46">
-        <v>3104.561460507158</v>
+        <v>3106.685356795554</v>
       </c>
       <c r="E46">
-        <v>529.216</v>
+        <v>561.7300000000001</v>
       </c>
       <c r="F46">
-        <v>1430.616</v>
+        <v>1463.13</v>
       </c>
       <c r="G46">
         <v>201</v>
@@ -5053,28 +5053,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M46">
-        <v>74.10590879999999</v>
+        <v>75.79013400000001</v>
       </c>
       <c r="N46">
-        <v>708.6496467555555</v>
+        <v>706.9654215555555</v>
       </c>
       <c r="O46">
-        <v>175.5695062840166</v>
+        <v>175.1522357919068</v>
       </c>
       <c r="P46">
-        <v>533.0801404715389</v>
+        <v>531.8131857636487</v>
       </c>
       <c r="Q46">
-        <v>723.8801404715389</v>
+        <v>722.6131857636487</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08480089795539997</v>
+        <v>0.08539958586340654</v>
       </c>
       <c r="T46">
-        <v>0.9007135786466505</v>
+        <v>0.9145400892241694</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.56266049807294</v>
+        <v>10.32793470922687</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06450466853263664</v>
+        <v>0.06437560226488098</v>
       </c>
       <c r="C47">
-        <v>1844.555356795554</v>
+        <v>1814.168161078293</v>
       </c>
       <c r="D47">
-        <v>3106.685356795554</v>
+        <v>3108.812161078293</v>
       </c>
       <c r="E47">
-        <v>561.7300000000001</v>
+        <v>594.244</v>
       </c>
       <c r="F47">
-        <v>1463.13</v>
+        <v>1495.644</v>
       </c>
       <c r="G47">
         <v>201</v>
@@ -5135,28 +5135,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M47">
-        <v>75.79013400000001</v>
+        <v>77.47435919999999</v>
       </c>
       <c r="N47">
-        <v>706.9654215555555</v>
+        <v>705.2811963555555</v>
       </c>
       <c r="O47">
-        <v>175.1522357919068</v>
+        <v>174.734965299797</v>
       </c>
       <c r="P47">
-        <v>531.8131857636487</v>
+        <v>530.5462310557584</v>
       </c>
       <c r="Q47">
-        <v>722.6131857636487</v>
+        <v>721.3462310557584</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08539958586340654</v>
+        <v>0.08602044739763556</v>
       </c>
       <c r="T47">
-        <v>0.9145400892241694</v>
+        <v>0.928878692786041</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.32793470922687</v>
+        <v>10.10341438946107</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06437560226488098</v>
+        <v>0.06424653599712533</v>
       </c>
       <c r="C48">
-        <v>1814.168161078293</v>
+        <v>1783.783879331815</v>
       </c>
       <c r="D48">
-        <v>3108.812161078293</v>
+        <v>3110.941879331815</v>
       </c>
       <c r="E48">
-        <v>594.244</v>
+        <v>626.7580000000002</v>
       </c>
       <c r="F48">
-        <v>1495.644</v>
+        <v>1528.158</v>
       </c>
       <c r="G48">
         <v>201</v>
@@ -5217,28 +5217,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M48">
-        <v>77.47435919999999</v>
+        <v>79.15858440000001</v>
       </c>
       <c r="N48">
-        <v>705.2811963555555</v>
+        <v>703.5969711555555</v>
       </c>
       <c r="O48">
-        <v>174.734965299797</v>
+        <v>174.3176948076873</v>
       </c>
       <c r="P48">
-        <v>530.5462310557584</v>
+        <v>529.2792763478682</v>
       </c>
       <c r="Q48">
-        <v>721.3462310557584</v>
+        <v>720.0792763478682</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08602044739763556</v>
+        <v>0.08666473766900533</v>
       </c>
       <c r="T48">
-        <v>0.928878692786041</v>
+        <v>0.9437583757276058</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.10341438946107</v>
+        <v>9.888448125855513</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06424653599712533</v>
+        <v>0.06473130393731197</v>
       </c>
       <c r="C49">
-        <v>1783.783879331815</v>
+        <v>1743.285803017465</v>
       </c>
       <c r="D49">
-        <v>3110.941879331815</v>
+        <v>3102.957803017466</v>
       </c>
       <c r="E49">
-        <v>626.7580000000002</v>
+        <v>659.2720000000003</v>
       </c>
       <c r="F49">
-        <v>1528.158</v>
+        <v>1560.672</v>
       </c>
       <c r="G49">
         <v>201</v>
@@ -5299,45 +5299,45 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M49">
-        <v>79.15858440000001</v>
+        <v>83.49595200000002</v>
       </c>
       <c r="N49">
-        <v>703.5969711555555</v>
+        <v>699.2596035555555</v>
       </c>
       <c r="O49">
-        <v>174.3176948076873</v>
+        <v>173.243102459281</v>
       </c>
       <c r="P49">
-        <v>529.2792763478682</v>
+        <v>526.0165010962744</v>
       </c>
       <c r="Q49">
-        <v>720.0792763478682</v>
+        <v>716.8165010962744</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08666473766900533</v>
+        <v>0.08733380833542777</v>
       </c>
       <c r="T49">
-        <v>0.9437583757276058</v>
+        <v>0.9592103541669231</v>
       </c>
       <c r="U49">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V49">
         <v>0.2477521961491617</v>
       </c>
       <c r="W49">
-        <v>0.03896643623947342</v>
+        <v>0.04024525750601984</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>9.888448125855513</v>
+        <v>9.37477251059495</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06473130393731197</v>
+        <v>0.06461502588222177</v>
       </c>
       <c r="C50">
-        <v>1743.285803017466</v>
+        <v>1712.683151839167</v>
       </c>
       <c r="D50">
-        <v>3102.957803017466</v>
+        <v>3104.869151839167</v>
       </c>
       <c r="E50">
-        <v>659.272</v>
+        <v>691.7859999999999</v>
       </c>
       <c r="F50">
-        <v>1560.672</v>
+        <v>1593.186</v>
       </c>
       <c r="G50">
         <v>201</v>
@@ -5381,28 +5381,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M50">
-        <v>83.495952</v>
+        <v>85.235451</v>
       </c>
       <c r="N50">
-        <v>699.2596035555555</v>
+        <v>697.5201045555555</v>
       </c>
       <c r="O50">
-        <v>173.243102459281</v>
+        <v>172.8121377618318</v>
       </c>
       <c r="P50">
-        <v>526.0165010962744</v>
+        <v>524.7079667937237</v>
       </c>
       <c r="Q50">
-        <v>716.8165010962744</v>
+        <v>715.5079667937237</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08733380833542777</v>
+        <v>0.0880291170672001</v>
       </c>
       <c r="T50">
-        <v>0.959210354166923</v>
+        <v>0.9752682925450371</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>9.37477251059495</v>
+        <v>9.183450622623624</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06461502588222177</v>
+        <v>0.06449874782713158</v>
       </c>
       <c r="C51">
-        <v>1712.683151839167</v>
+        <v>1682.082856803783</v>
       </c>
       <c r="D51">
-        <v>3104.869151839167</v>
+        <v>3106.782856803783</v>
       </c>
       <c r="E51">
-        <v>691.7859999999999</v>
+        <v>724.3000000000001</v>
       </c>
       <c r="F51">
-        <v>1593.186</v>
+        <v>1625.7</v>
       </c>
       <c r="G51">
         <v>201</v>
@@ -5463,28 +5463,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M51">
-        <v>85.235451</v>
+        <v>86.97495000000001</v>
       </c>
       <c r="N51">
-        <v>697.5201045555555</v>
+        <v>695.7806055555554</v>
       </c>
       <c r="O51">
-        <v>172.8121377618318</v>
+        <v>172.3811730643825</v>
       </c>
       <c r="P51">
-        <v>524.7079667937237</v>
+        <v>523.399432491173</v>
       </c>
       <c r="Q51">
-        <v>715.5079667937237</v>
+        <v>714.199432491173</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0880291170672001</v>
+        <v>0.08875223814824333</v>
       </c>
       <c r="T51">
-        <v>0.9752682925450371</v>
+        <v>0.9919685484582756</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>9.183450622623624</v>
+        <v>8.999781610171151</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06449874782713158</v>
+        <v>0.0643824697720414</v>
       </c>
       <c r="C52">
-        <v>1682.082856803783</v>
+        <v>1651.484922270673</v>
       </c>
       <c r="D52">
-        <v>3106.782856803783</v>
+        <v>3108.698922270673</v>
       </c>
       <c r="E52">
-        <v>724.3000000000001</v>
+        <v>756.8140000000002</v>
       </c>
       <c r="F52">
-        <v>1625.7</v>
+        <v>1658.214</v>
       </c>
       <c r="G52">
         <v>201</v>
@@ -5545,28 +5545,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M52">
-        <v>86.97495000000001</v>
+        <v>88.714449</v>
       </c>
       <c r="N52">
-        <v>695.7806055555554</v>
+        <v>694.0411065555554</v>
       </c>
       <c r="O52">
-        <v>172.3811730643825</v>
+        <v>171.9502083669332</v>
       </c>
       <c r="P52">
-        <v>523.399432491173</v>
+        <v>522.0908981886222</v>
       </c>
       <c r="Q52">
-        <v>714.199432491173</v>
+        <v>712.8908981886223</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08875223814824333</v>
+        <v>0.0895048743754516</v>
       </c>
       <c r="T52">
-        <v>0.9919685484582756</v>
+        <v>1.009350447470014</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.999781610171151</v>
+        <v>8.823315304089364</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0643824697720414</v>
+        <v>0.06426619171695122</v>
       </c>
       <c r="C53">
-        <v>1651.484922270673</v>
+        <v>1620.889352609951</v>
       </c>
       <c r="D53">
-        <v>3108.698922270673</v>
+        <v>3110.617352609951</v>
       </c>
       <c r="E53">
-        <v>756.8140000000002</v>
+        <v>789.3280000000001</v>
       </c>
       <c r="F53">
-        <v>1658.214</v>
+        <v>1690.728</v>
       </c>
       <c r="G53">
         <v>201</v>
@@ -5627,28 +5627,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M53">
-        <v>88.714449</v>
+        <v>90.453948</v>
       </c>
       <c r="N53">
-        <v>694.0411065555554</v>
+        <v>692.3016075555555</v>
       </c>
       <c r="O53">
-        <v>171.9502083669332</v>
+        <v>171.519243669484</v>
       </c>
       <c r="P53">
-        <v>522.0908981886222</v>
+        <v>520.7823638860716</v>
       </c>
       <c r="Q53">
-        <v>712.8908981886223</v>
+        <v>711.5823638860716</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0895048743754516</v>
+        <v>0.09028887044546022</v>
       </c>
       <c r="T53">
-        <v>1.009350447470014</v>
+        <v>1.027456592273908</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.823315304089364</v>
+        <v>8.653636163626109</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06426619171695122</v>
+        <v>0.06414991366186103</v>
       </c>
       <c r="C54">
-        <v>1620.889352609951</v>
+        <v>1590.29615220253</v>
       </c>
       <c r="D54">
-        <v>3110.617352609951</v>
+        <v>3112.53815220253</v>
       </c>
       <c r="E54">
-        <v>789.3280000000001</v>
+        <v>821.8420000000002</v>
       </c>
       <c r="F54">
-        <v>1690.728</v>
+        <v>1723.242</v>
       </c>
       <c r="G54">
         <v>201</v>
@@ -5709,28 +5709,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M54">
-        <v>90.453948</v>
+        <v>92.19344700000001</v>
       </c>
       <c r="N54">
-        <v>692.3016075555555</v>
+        <v>690.5621085555555</v>
       </c>
       <c r="O54">
-        <v>171.519243669484</v>
+        <v>171.0882789720347</v>
       </c>
       <c r="P54">
-        <v>520.7823638860716</v>
+        <v>519.4738295835208</v>
       </c>
       <c r="Q54">
-        <v>711.5823638860716</v>
+        <v>710.2738295835209</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09028887044546022</v>
+        <v>0.09110622805036279</v>
       </c>
       <c r="T54">
-        <v>1.027456592273908</v>
+        <v>1.046333211324776</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.653636163626109</v>
+        <v>8.490360009595427</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06414991366186103</v>
+        <v>0.06403363560677083</v>
       </c>
       <c r="C55">
-        <v>1590.29615220253</v>
+        <v>1559.705325440147</v>
       </c>
       <c r="D55">
-        <v>3112.53815220253</v>
+        <v>3114.461325440147</v>
       </c>
       <c r="E55">
-        <v>821.8420000000002</v>
+        <v>854.3560000000001</v>
       </c>
       <c r="F55">
-        <v>1723.242</v>
+        <v>1755.756</v>
       </c>
       <c r="G55">
         <v>201</v>
@@ -5791,28 +5791,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M55">
-        <v>92.19344700000001</v>
+        <v>93.932946</v>
       </c>
       <c r="N55">
-        <v>690.5621085555555</v>
+        <v>688.8226095555555</v>
       </c>
       <c r="O55">
-        <v>171.0882789720347</v>
+        <v>170.6573142745854</v>
       </c>
       <c r="P55">
-        <v>519.4738295835208</v>
+        <v>518.16529528097</v>
       </c>
       <c r="Q55">
-        <v>710.2738295835209</v>
+        <v>708.9652952809699</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09110622805036279</v>
+        <v>0.09195912294243505</v>
       </c>
       <c r="T55">
-        <v>1.046333211324776</v>
+        <v>1.066030552943073</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.490360009595427</v>
+        <v>8.333131120528844</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06403363560677083</v>
+        <v>0.06391735755168065</v>
       </c>
       <c r="C56">
-        <v>1559.705325440147</v>
+        <v>1529.116876725403</v>
       </c>
       <c r="D56">
-        <v>3114.461325440147</v>
+        <v>3116.386876725403</v>
       </c>
       <c r="E56">
-        <v>854.3560000000001</v>
+        <v>886.8700000000002</v>
       </c>
       <c r="F56">
-        <v>1755.756</v>
+        <v>1788.27</v>
       </c>
       <c r="G56">
         <v>201</v>
@@ -5873,28 +5873,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M56">
-        <v>93.932946</v>
+        <v>95.67244500000001</v>
       </c>
       <c r="N56">
-        <v>688.8226095555555</v>
+        <v>687.0831105555554</v>
       </c>
       <c r="O56">
-        <v>170.6573142745854</v>
+        <v>170.2263495771361</v>
       </c>
       <c r="P56">
-        <v>518.16529528097</v>
+        <v>516.8567609784193</v>
       </c>
       <c r="Q56">
-        <v>708.9652952809699</v>
+        <v>707.6567609784192</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09195912294243505</v>
+        <v>0.09284992427415498</v>
       </c>
       <c r="T56">
-        <v>1.066030552943073</v>
+        <v>1.086603331966628</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.333131120528844</v>
+        <v>8.181619645610137</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06391735755168065</v>
+        <v>0.06380107949659047</v>
       </c>
       <c r="C57">
-        <v>1529.116876725403</v>
+        <v>1498.530810471789</v>
       </c>
       <c r="D57">
-        <v>3116.386876725403</v>
+        <v>3118.31481047179</v>
       </c>
       <c r="E57">
-        <v>886.8700000000002</v>
+        <v>919.3840000000004</v>
       </c>
       <c r="F57">
-        <v>1788.27</v>
+        <v>1820.784</v>
       </c>
       <c r="G57">
         <v>201</v>
@@ -5955,28 +5955,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M57">
-        <v>95.67244500000001</v>
+        <v>97.41194400000002</v>
       </c>
       <c r="N57">
-        <v>687.0831105555554</v>
+        <v>685.3436115555554</v>
       </c>
       <c r="O57">
-        <v>170.2263495771361</v>
+        <v>169.7953848796868</v>
       </c>
       <c r="P57">
-        <v>516.8567609784193</v>
+        <v>515.5482266758686</v>
       </c>
       <c r="Q57">
-        <v>707.6567609784192</v>
+        <v>706.3482266758685</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09284992427415498</v>
+        <v>0.09378121657549854</v>
       </c>
       <c r="T57">
-        <v>1.086603331966628</v>
+        <v>1.108111237309435</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.181619645610137</v>
+        <v>8.03551929479567</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06380107949659047</v>
+        <v>0.06368480144150028</v>
       </c>
       <c r="C58">
-        <v>1498.530810471789</v>
+        <v>1467.947131103732</v>
       </c>
       <c r="D58">
-        <v>3118.31481047179</v>
+        <v>3120.245131103732</v>
       </c>
       <c r="E58">
-        <v>919.3840000000004</v>
+        <v>951.8980000000003</v>
       </c>
       <c r="F58">
-        <v>1820.784</v>
+        <v>1853.298</v>
       </c>
       <c r="G58">
         <v>201</v>
@@ -6037,28 +6037,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M58">
-        <v>97.41194400000002</v>
+        <v>99.15144300000001</v>
       </c>
       <c r="N58">
-        <v>685.3436115555554</v>
+        <v>683.6041125555555</v>
       </c>
       <c r="O58">
-        <v>169.7953848796868</v>
+        <v>169.3644201822376</v>
       </c>
       <c r="P58">
-        <v>515.5482266758686</v>
+        <v>514.2396923733179</v>
       </c>
       <c r="Q58">
-        <v>706.3482266758685</v>
+        <v>705.0396923733178</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09378121657549854</v>
+        <v>0.09475582479783481</v>
       </c>
       <c r="T58">
-        <v>1.108111237309435</v>
+        <v>1.130619510342606</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.03551929479567</v>
+        <v>7.894545272079958</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06368480144150028</v>
+        <v>0.06356852338641009</v>
       </c>
       <c r="C59">
-        <v>1467.947131103732</v>
+        <v>1437.365843056612</v>
       </c>
       <c r="D59">
-        <v>3120.245131103732</v>
+        <v>3122.177843056613</v>
       </c>
       <c r="E59">
-        <v>951.8980000000003</v>
+        <v>984.4120000000004</v>
       </c>
       <c r="F59">
-        <v>1853.298</v>
+        <v>1885.812</v>
       </c>
       <c r="G59">
         <v>201</v>
@@ -6119,28 +6119,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M59">
-        <v>99.15144300000001</v>
+        <v>100.890942</v>
       </c>
       <c r="N59">
-        <v>683.6041125555555</v>
+        <v>681.8646135555555</v>
       </c>
       <c r="O59">
-        <v>169.3644201822376</v>
+        <v>168.9334554847883</v>
       </c>
       <c r="P59">
-        <v>514.2396923733179</v>
+        <v>512.9311580707672</v>
       </c>
       <c r="Q59">
-        <v>705.0396923733178</v>
+        <v>703.7311580707672</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09475582479783481</v>
+        <v>0.09577684293552044</v>
       </c>
       <c r="T59">
-        <v>1.130619510342606</v>
+        <v>1.154199605901165</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.894545272079958</v>
+        <v>7.758432422561337</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0635685233864101</v>
+        <v>0.06345224533131991</v>
       </c>
       <c r="C60">
-        <v>1437.365843056613</v>
+        <v>1406.786950776813</v>
       </c>
       <c r="D60">
-        <v>3122.177843056613</v>
+        <v>3124.112950776813</v>
       </c>
       <c r="E60">
-        <v>984.4119999999999</v>
+        <v>1016.926</v>
       </c>
       <c r="F60">
-        <v>1885.812</v>
+        <v>1918.326</v>
       </c>
       <c r="G60">
         <v>201</v>
@@ -6201,28 +6201,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M60">
-        <v>100.890942</v>
+        <v>102.630441</v>
       </c>
       <c r="N60">
-        <v>681.8646135555555</v>
+        <v>680.1251145555555</v>
       </c>
       <c r="O60">
-        <v>168.9334554847883</v>
+        <v>168.5024907873391</v>
       </c>
       <c r="P60">
-        <v>512.9311580707672</v>
+        <v>511.6226237682164</v>
       </c>
       <c r="Q60">
-        <v>703.7311580707672</v>
+        <v>702.4226237682165</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09577684293552044</v>
+        <v>0.09684766683601997</v>
       </c>
       <c r="T60">
-        <v>1.154199605901165</v>
+        <v>1.178929950023556</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.758432422561339</v>
+        <v>7.626933567941654</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06345224533131991</v>
+        <v>0.06369704622207813</v>
       </c>
       <c r="C61">
-        <v>1406.786950776813</v>
+        <v>1370.201744123623</v>
       </c>
       <c r="D61">
-        <v>3124.112950776813</v>
+        <v>3120.041744123623</v>
       </c>
       <c r="E61">
-        <v>1016.926</v>
+        <v>1049.44</v>
       </c>
       <c r="F61">
-        <v>1918.326</v>
+        <v>1950.84</v>
       </c>
       <c r="G61">
         <v>201</v>
@@ -6283,45 +6283,45 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M61">
-        <v>102.630441</v>
+        <v>105.930612</v>
       </c>
       <c r="N61">
-        <v>680.1251145555555</v>
+        <v>676.8249435555555</v>
       </c>
       <c r="O61">
-        <v>168.5024907873391</v>
+        <v>167.6848661744213</v>
       </c>
       <c r="P61">
-        <v>511.6226237682164</v>
+        <v>509.1400773811342</v>
       </c>
       <c r="Q61">
-        <v>702.4226237682165</v>
+        <v>699.9400773811342</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09684766683601997</v>
+        <v>0.09797203193154452</v>
       </c>
       <c r="T61">
-        <v>1.178929950023556</v>
+        <v>1.204896811352068</v>
       </c>
       <c r="U61">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V61">
         <v>0.2477521961491617</v>
       </c>
       <c r="W61">
-        <v>0.04024525750601984</v>
+        <v>0.04084705574910052</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y61">
-        <v>7.626933567941654</v>
+        <v>7.389323452181656</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06369704622207813</v>
+        <v>0.06358678614941875</v>
       </c>
       <c r="C62">
-        <v>1370.201744123623</v>
+        <v>1339.520130650961</v>
       </c>
       <c r="D62">
-        <v>3120.041744123623</v>
+        <v>3121.874130650961</v>
       </c>
       <c r="E62">
-        <v>1049.44</v>
+        <v>1081.954</v>
       </c>
       <c r="F62">
-        <v>1950.84</v>
+        <v>1983.354</v>
       </c>
       <c r="G62">
         <v>201</v>
@@ -6365,28 +6365,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M62">
-        <v>105.930612</v>
+        <v>107.6961222</v>
       </c>
       <c r="N62">
-        <v>676.8249435555555</v>
+        <v>675.0594333555555</v>
       </c>
       <c r="O62">
-        <v>167.6848661744213</v>
+        <v>167.2474571450475</v>
       </c>
       <c r="P62">
-        <v>509.1400773811342</v>
+        <v>507.811976210508</v>
       </c>
       <c r="Q62">
-        <v>699.9400773811342</v>
+        <v>698.6119762105079</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09797203193154452</v>
+        <v>0.0991540567755575</v>
       </c>
       <c r="T62">
-        <v>1.204896811352068</v>
+        <v>1.232195306594861</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.389323452181656</v>
+        <v>7.26818700214589</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06358678614941875</v>
+        <v>0.06347652607675935</v>
       </c>
       <c r="C63">
-        <v>1339.520130650961</v>
+        <v>1308.840670747866</v>
       </c>
       <c r="D63">
-        <v>3121.874130650961</v>
+        <v>3123.708670747866</v>
       </c>
       <c r="E63">
-        <v>1081.954</v>
+        <v>1114.468</v>
       </c>
       <c r="F63">
-        <v>1983.354</v>
+        <v>2015.868</v>
       </c>
       <c r="G63">
         <v>201</v>
@@ -6447,28 +6447,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M63">
-        <v>107.6961222</v>
+        <v>109.4616324</v>
       </c>
       <c r="N63">
-        <v>675.0594333555555</v>
+        <v>673.2939231555555</v>
       </c>
       <c r="O63">
-        <v>167.2474571450475</v>
+        <v>166.8100481156738</v>
       </c>
       <c r="P63">
-        <v>507.811976210508</v>
+        <v>506.4838750398817</v>
       </c>
       <c r="Q63">
-        <v>698.6119762105079</v>
+        <v>697.2838750398817</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.0991540567755575</v>
+        <v>0.1003982934534659</v>
       </c>
       <c r="T63">
-        <v>1.232195306594861</v>
+        <v>1.260930564745171</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.26818700214589</v>
+        <v>7.150958179530634</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06347652607675935</v>
+        <v>0.06336626600409997</v>
       </c>
       <c r="C64">
-        <v>1308.840670747866</v>
+        <v>1278.163368213142</v>
       </c>
       <c r="D64">
-        <v>3123.708670747866</v>
+        <v>3125.545368213142</v>
       </c>
       <c r="E64">
-        <v>1114.468</v>
+        <v>1146.982</v>
       </c>
       <c r="F64">
-        <v>2015.868</v>
+        <v>2048.382</v>
       </c>
       <c r="G64">
         <v>201</v>
@@ -6529,28 +6529,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M64">
-        <v>109.4616324</v>
+        <v>111.2271426</v>
       </c>
       <c r="N64">
-        <v>673.2939231555555</v>
+        <v>671.5284129555555</v>
       </c>
       <c r="O64">
-        <v>166.8100481156738</v>
+        <v>166.3726390863001</v>
       </c>
       <c r="P64">
-        <v>506.4838750398817</v>
+        <v>505.1557738692554</v>
       </c>
       <c r="Q64">
-        <v>697.2838750398817</v>
+        <v>695.9557738692554</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1003982934534659</v>
+        <v>0.101709786168018</v>
       </c>
       <c r="T64">
-        <v>1.260930564745171</v>
+        <v>1.291219080092794</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.150958179530634</v>
+        <v>7.037450906839672</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06336626600409997</v>
+        <v>0.0632560059314406</v>
       </c>
       <c r="C65">
-        <v>1278.163368213142</v>
+        <v>1247.488226854538</v>
       </c>
       <c r="D65">
-        <v>3125.545368213142</v>
+        <v>3127.384226854539</v>
       </c>
       <c r="E65">
-        <v>1146.982</v>
+        <v>1179.496</v>
       </c>
       <c r="F65">
-        <v>2048.382</v>
+        <v>2080.896</v>
       </c>
       <c r="G65">
         <v>201</v>
@@ -6611,28 +6611,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M65">
-        <v>111.2271426</v>
+        <v>112.9926528</v>
       </c>
       <c r="N65">
-        <v>671.5284129555555</v>
+        <v>669.7629027555555</v>
       </c>
       <c r="O65">
-        <v>166.3726390863001</v>
+        <v>165.9352300569263</v>
       </c>
       <c r="P65">
-        <v>505.1557738692554</v>
+        <v>503.8276726986292</v>
       </c>
       <c r="Q65">
-        <v>695.9557738692554</v>
+        <v>694.6276726986291</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.101709786168018</v>
+        <v>0.1030941395889341</v>
       </c>
       <c r="T65">
-        <v>1.291219080092794</v>
+        <v>1.323190290737508</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.037450906839672</v>
+        <v>6.927490736420301</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0632560059314406</v>
+        <v>0.06314574585878122</v>
       </c>
       <c r="C66">
-        <v>1247.488226854538</v>
+        <v>1216.815250488768</v>
       </c>
       <c r="D66">
-        <v>3127.384226854539</v>
+        <v>3129.225250488769</v>
       </c>
       <c r="E66">
-        <v>1179.496</v>
+        <v>1212.01</v>
       </c>
       <c r="F66">
-        <v>2080.896</v>
+        <v>2113.41</v>
       </c>
       <c r="G66">
         <v>201</v>
@@ -6693,28 +6693,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M66">
-        <v>112.9926528</v>
+        <v>114.758163</v>
       </c>
       <c r="N66">
-        <v>669.7629027555555</v>
+        <v>667.9973925555555</v>
       </c>
       <c r="O66">
-        <v>165.9352300569263</v>
+        <v>165.4978210275526</v>
       </c>
       <c r="P66">
-        <v>503.8276726986292</v>
+        <v>502.4995715280029</v>
       </c>
       <c r="Q66">
-        <v>694.6276726986291</v>
+        <v>693.299571528003</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1030941395889341</v>
+        <v>0.1045575989196168</v>
       </c>
       <c r="T66">
-        <v>1.323190290737508</v>
+        <v>1.356988427704776</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.927490736420301</v>
+        <v>6.820913955859988</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06314574585878122</v>
+        <v>0.06303548578612184</v>
       </c>
       <c r="C67">
-        <v>1216.815250488768</v>
+        <v>1186.144442941537</v>
       </c>
       <c r="D67">
-        <v>3129.225250488769</v>
+        <v>3131.068442941537</v>
       </c>
       <c r="E67">
-        <v>1212.01</v>
+        <v>1244.524</v>
       </c>
       <c r="F67">
-        <v>2113.41</v>
+        <v>2145.924</v>
       </c>
       <c r="G67">
         <v>201</v>
@@ -6775,28 +6775,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M67">
-        <v>114.758163</v>
+        <v>116.5236732</v>
       </c>
       <c r="N67">
-        <v>667.9973925555555</v>
+        <v>666.2318823555555</v>
       </c>
       <c r="O67">
-        <v>165.4978210275526</v>
+        <v>165.0604119981788</v>
       </c>
       <c r="P67">
-        <v>502.4995715280029</v>
+        <v>501.1714703573767</v>
       </c>
       <c r="Q67">
-        <v>693.299571528003</v>
+        <v>691.9714703573767</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1045575989196168</v>
+        <v>0.1061071440932809</v>
       </c>
       <c r="T67">
-        <v>1.356988427704776</v>
+        <v>1.392774690376002</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.820913955859988</v>
+        <v>6.717566774710596</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06303548578612184</v>
+        <v>0.06292522571346246</v>
       </c>
       <c r="C68">
-        <v>1186.144442941537</v>
+        <v>1155.475808047569</v>
       </c>
       <c r="D68">
-        <v>3131.068442941537</v>
+        <v>3132.91380804757</v>
       </c>
       <c r="E68">
-        <v>1244.524</v>
+        <v>1277.038</v>
       </c>
       <c r="F68">
-        <v>2145.924</v>
+        <v>2178.438</v>
       </c>
       <c r="G68">
         <v>201</v>
@@ -6857,28 +6857,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M68">
-        <v>116.5236732</v>
+        <v>118.2891834</v>
       </c>
       <c r="N68">
-        <v>666.2318823555555</v>
+        <v>664.4663721555555</v>
       </c>
       <c r="O68">
-        <v>165.0604119981788</v>
+        <v>164.6230029688051</v>
       </c>
       <c r="P68">
-        <v>501.1714703573767</v>
+        <v>499.8433691867505</v>
       </c>
       <c r="Q68">
-        <v>691.9714703573767</v>
+        <v>690.6433691867505</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1061071440932809</v>
+        <v>0.1077506010956518</v>
       </c>
       <c r="T68">
-        <v>1.392774690376002</v>
+        <v>1.430729817451544</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.717566774710596</v>
+        <v>6.617304584043273</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06292522571346246</v>
+        <v>0.06281496564080308</v>
       </c>
       <c r="C69">
-        <v>1155.475808047569</v>
+        <v>1124.809349650636</v>
       </c>
       <c r="D69">
-        <v>3132.91380804757</v>
+        <v>3134.761349650636</v>
       </c>
       <c r="E69">
-        <v>1277.038</v>
+        <v>1309.552</v>
       </c>
       <c r="F69">
-        <v>2178.438</v>
+        <v>2210.952</v>
       </c>
       <c r="G69">
         <v>201</v>
@@ -6939,28 +6939,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M69">
-        <v>118.2891834</v>
+        <v>120.0546936</v>
       </c>
       <c r="N69">
-        <v>664.4663721555555</v>
+        <v>662.7008619555554</v>
       </c>
       <c r="O69">
-        <v>164.6230029688051</v>
+        <v>164.1855939394313</v>
       </c>
       <c r="P69">
-        <v>499.8433691867505</v>
+        <v>498.5152680161241</v>
       </c>
       <c r="Q69">
-        <v>690.6433691867505</v>
+        <v>689.315268016124</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1077506010956518</v>
+        <v>0.109496774160671</v>
       </c>
       <c r="T69">
-        <v>1.430729817451544</v>
+        <v>1.471057139969308</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.617304584043273</v>
+        <v>6.519991281336753</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06281496564080308</v>
+        <v>0.0627047055681437</v>
       </c>
       <c r="C70">
-        <v>1124.809349650636</v>
+        <v>1094.145071603581</v>
       </c>
       <c r="D70">
-        <v>3134.761349650636</v>
+        <v>3136.611071603581</v>
       </c>
       <c r="E70">
-        <v>1309.552</v>
+        <v>1342.066</v>
       </c>
       <c r="F70">
-        <v>2210.952</v>
+        <v>2243.466</v>
       </c>
       <c r="G70">
         <v>201</v>
@@ -7021,28 +7021,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M70">
-        <v>120.0546936</v>
+        <v>121.8202038</v>
       </c>
       <c r="N70">
-        <v>662.7008619555554</v>
+        <v>660.9353517555554</v>
       </c>
       <c r="O70">
-        <v>164.1855939394313</v>
+        <v>163.7481849100576</v>
       </c>
       <c r="P70">
-        <v>498.5152680161241</v>
+        <v>497.1871668454978</v>
       </c>
       <c r="Q70">
-        <v>689.315268016124</v>
+        <v>687.9871668454978</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.109496774160671</v>
+        <v>0.1113556035524656</v>
       </c>
       <c r="T70">
-        <v>1.471057139969308</v>
+        <v>1.513986225230153</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.519991281336753</v>
+        <v>6.425498654071004</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0627047055681437</v>
+        <v>0.06259444549548432</v>
       </c>
       <c r="C71">
-        <v>1094.145071603581</v>
+        <v>1063.482977768344</v>
       </c>
       <c r="D71">
-        <v>3136.611071603581</v>
+        <v>3138.462977768345</v>
       </c>
       <c r="E71">
-        <v>1342.066</v>
+        <v>1374.58</v>
       </c>
       <c r="F71">
-        <v>2243.466</v>
+        <v>2275.98</v>
       </c>
       <c r="G71">
         <v>201</v>
@@ -7103,28 +7103,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M71">
-        <v>121.8202038</v>
+        <v>123.585714</v>
       </c>
       <c r="N71">
-        <v>660.9353517555554</v>
+        <v>659.1698415555554</v>
       </c>
       <c r="O71">
-        <v>163.7481849100576</v>
+        <v>163.3107758806838</v>
       </c>
       <c r="P71">
-        <v>497.1871668454978</v>
+        <v>495.8590656748716</v>
       </c>
       <c r="Q71">
-        <v>687.9871668454978</v>
+        <v>686.6590656748716</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1113556035524656</v>
+        <v>0.1133383549037132</v>
       </c>
       <c r="T71">
-        <v>1.513986225230153</v>
+        <v>1.559777249508388</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.425498654071004</v>
+        <v>6.333705816155703</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06259444549548432</v>
+        <v>0.06248418542282493</v>
       </c>
       <c r="C72">
-        <v>1063.482977768344</v>
+        <v>1032.823072015996</v>
       </c>
       <c r="D72">
-        <v>3138.462977768345</v>
+        <v>3140.317072015996</v>
       </c>
       <c r="E72">
-        <v>1374.58</v>
+        <v>1407.094</v>
       </c>
       <c r="F72">
-        <v>2275.98</v>
+        <v>2308.494</v>
       </c>
       <c r="G72">
         <v>201</v>
@@ -7185,28 +7185,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M72">
-        <v>123.585714</v>
+        <v>125.3512242</v>
       </c>
       <c r="N72">
-        <v>659.1698415555554</v>
+        <v>657.4043313555554</v>
       </c>
       <c r="O72">
-        <v>163.3107758806838</v>
+        <v>162.8733668513101</v>
       </c>
       <c r="P72">
-        <v>495.8590656748716</v>
+        <v>494.5309645042454</v>
       </c>
       <c r="Q72">
-        <v>686.6590656748716</v>
+        <v>685.3309645042455</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1133383549037132</v>
+        <v>0.1154578477274606</v>
       </c>
       <c r="T72">
-        <v>1.559777249508388</v>
+        <v>1.608726275460984</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.333705816155703</v>
+        <v>6.244498691984496</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06248418542282494</v>
+        <v>0.06237392535016556</v>
       </c>
       <c r="C73">
-        <v>1032.823072015996</v>
+        <v>1002.165358226756</v>
       </c>
       <c r="D73">
-        <v>3140.317072015996</v>
+        <v>3142.173358226756</v>
       </c>
       <c r="E73">
-        <v>1407.094</v>
+        <v>1439.608</v>
       </c>
       <c r="F73">
-        <v>2308.494</v>
+        <v>2341.008</v>
       </c>
       <c r="G73">
         <v>201</v>
@@ -7267,28 +7267,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M73">
-        <v>125.3512242</v>
+        <v>127.1167344</v>
       </c>
       <c r="N73">
-        <v>657.4043313555554</v>
+        <v>655.6388211555554</v>
       </c>
       <c r="O73">
-        <v>162.8733668513101</v>
+        <v>162.4359578219363</v>
       </c>
       <c r="P73">
-        <v>494.5309645042454</v>
+        <v>493.2028633336191</v>
       </c>
       <c r="Q73">
-        <v>685.3309645042455</v>
+        <v>684.0028633336192</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1154578477274606</v>
+        <v>0.1177287328957614</v>
       </c>
       <c r="T73">
-        <v>1.608726275460983</v>
+        <v>1.661171660410193</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.244498691984496</v>
+        <v>6.157769543484712</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06237392535016556</v>
+        <v>0.06281280617431728</v>
       </c>
       <c r="C74">
-        <v>1002.165358226756</v>
+        <v>962.2755558945883</v>
       </c>
       <c r="D74">
-        <v>3142.173358226756</v>
+        <v>3134.797555894588</v>
       </c>
       <c r="E74">
-        <v>1439.608</v>
+        <v>1472.122</v>
       </c>
       <c r="F74">
-        <v>2341.008</v>
+        <v>2373.522</v>
       </c>
       <c r="G74">
         <v>201</v>
@@ -7349,45 +7349,45 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M74">
-        <v>127.1167344</v>
+        <v>131.2557666</v>
       </c>
       <c r="N74">
-        <v>655.6388211555554</v>
+        <v>651.4997889555555</v>
       </c>
       <c r="O74">
-        <v>162.4359578219363</v>
+        <v>161.4105035044542</v>
       </c>
       <c r="P74">
-        <v>493.2028633336191</v>
+        <v>490.0892854511012</v>
       </c>
       <c r="Q74">
-        <v>684.0028633336192</v>
+        <v>680.8892854511012</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1177287328957614</v>
+        <v>0.1201678317802326</v>
       </c>
       <c r="T74">
-        <v>1.661171660410193</v>
+        <v>1.717501888688974</v>
       </c>
       <c r="U74">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V74">
         <v>0.2477521961491617</v>
       </c>
       <c r="W74">
-        <v>0.04084705574910052</v>
+        <v>0.04159930355295136</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>6.157769543484712</v>
+        <v>5.963589835568836</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06281280617431728</v>
+        <v>0.06271006857969641</v>
       </c>
       <c r="C75">
-        <v>962.2755558945883</v>
+        <v>931.4850512670159</v>
       </c>
       <c r="D75">
-        <v>3134.797555894588</v>
+        <v>3136.521051267016</v>
       </c>
       <c r="E75">
-        <v>1472.122</v>
+        <v>1504.636</v>
       </c>
       <c r="F75">
-        <v>2373.522</v>
+        <v>2406.036</v>
       </c>
       <c r="G75">
         <v>201</v>
@@ -7431,28 +7431,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M75">
-        <v>131.2557666</v>
+        <v>133.0537908</v>
       </c>
       <c r="N75">
-        <v>651.4997889555555</v>
+        <v>649.7017647555555</v>
       </c>
       <c r="O75">
-        <v>161.4105035044542</v>
+        <v>160.9650390601749</v>
       </c>
       <c r="P75">
-        <v>490.0892854511012</v>
+        <v>488.7367256953805</v>
       </c>
       <c r="Q75">
-        <v>680.8892854511012</v>
+        <v>679.5367256953805</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1201678317802326</v>
+        <v>0.122794553655817</v>
       </c>
       <c r="T75">
-        <v>1.717501888688974</v>
+        <v>1.778165211450738</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.963589835568836</v>
+        <v>5.883000783736824</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06271006857969641</v>
+        <v>0.06260733098507554</v>
       </c>
       <c r="C76">
-        <v>931.4850512670159</v>
+        <v>900.6964428195151</v>
       </c>
       <c r="D76">
-        <v>3136.521051267016</v>
+        <v>3138.246442819515</v>
       </c>
       <c r="E76">
-        <v>1504.636</v>
+        <v>1537.15</v>
       </c>
       <c r="F76">
-        <v>2406.036</v>
+        <v>2438.55</v>
       </c>
       <c r="G76">
         <v>201</v>
@@ -7513,28 +7513,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M76">
-        <v>133.0537908</v>
+        <v>134.851815</v>
       </c>
       <c r="N76">
-        <v>649.7017647555555</v>
+        <v>647.9037405555555</v>
       </c>
       <c r="O76">
-        <v>160.9650390601749</v>
+        <v>160.5195746158956</v>
       </c>
       <c r="P76">
-        <v>488.7367256953805</v>
+        <v>487.3841659396599</v>
       </c>
       <c r="Q76">
-        <v>679.5367256953805</v>
+        <v>678.1841659396599</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.122794553655817</v>
+        <v>0.1256314132814481</v>
       </c>
       <c r="T76">
-        <v>1.778165211450738</v>
+        <v>1.843681600033444</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.883000783736824</v>
+        <v>5.804560773286999</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06260733098507554</v>
+        <v>0.06250459339045467</v>
       </c>
       <c r="C77">
-        <v>900.6964428195151</v>
+        <v>869.9097336830596</v>
       </c>
       <c r="D77">
-        <v>3138.246442819515</v>
+        <v>3139.97373368306</v>
       </c>
       <c r="E77">
-        <v>1537.15</v>
+        <v>1569.664</v>
       </c>
       <c r="F77">
-        <v>2438.55</v>
+        <v>2471.064</v>
       </c>
       <c r="G77">
         <v>201</v>
@@ -7595,28 +7595,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M77">
-        <v>134.851815</v>
+        <v>136.6498392</v>
       </c>
       <c r="N77">
-        <v>647.9037405555555</v>
+        <v>646.1057163555554</v>
       </c>
       <c r="O77">
-        <v>160.5195746158956</v>
+        <v>160.0741101716162</v>
       </c>
       <c r="P77">
-        <v>487.3841659396599</v>
+        <v>486.0316061839392</v>
       </c>
       <c r="Q77">
-        <v>678.1841659396599</v>
+        <v>676.8316061839391</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1256314132814481</v>
+        <v>0.1287046778758818</v>
       </c>
       <c r="T77">
-        <v>1.843681600033444</v>
+        <v>1.914657687664708</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.804560773286999</v>
+        <v>5.728184973638485</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.06250459339045467</v>
+        <v>0.06240185579583379</v>
       </c>
       <c r="C78">
-        <v>869.9097336830596</v>
+        <v>839.1249269955183</v>
       </c>
       <c r="D78">
-        <v>3139.97373368306</v>
+        <v>3141.702926995518</v>
       </c>
       <c r="E78">
-        <v>1569.664</v>
+        <v>1602.178</v>
       </c>
       <c r="F78">
-        <v>2471.064</v>
+        <v>2503.578</v>
       </c>
       <c r="G78">
         <v>201</v>
@@ -7677,28 +7677,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M78">
-        <v>136.6498392</v>
+        <v>138.4478634</v>
       </c>
       <c r="N78">
-        <v>646.1057163555554</v>
+        <v>644.3076921555555</v>
       </c>
       <c r="O78">
-        <v>160.0741101716162</v>
+        <v>159.6286457273369</v>
       </c>
       <c r="P78">
-        <v>486.0316061839392</v>
+        <v>484.6790464282186</v>
       </c>
       <c r="Q78">
-        <v>676.8316061839391</v>
+        <v>675.4790464282187</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1287046778758818</v>
+        <v>0.1320451828698315</v>
       </c>
       <c r="T78">
-        <v>1.914657687664708</v>
+        <v>1.991805609003038</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.728184973638485</v>
+        <v>5.653792960993831</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.06240185579583379</v>
+        <v>0.06229911820121292</v>
       </c>
       <c r="C79">
-        <v>839.1249269955183</v>
+        <v>808.3420259016757</v>
       </c>
       <c r="D79">
-        <v>3141.702926995518</v>
+        <v>3143.434025901676</v>
       </c>
       <c r="E79">
-        <v>1602.178</v>
+        <v>1634.692</v>
       </c>
       <c r="F79">
-        <v>2503.578</v>
+        <v>2536.092</v>
       </c>
       <c r="G79">
         <v>201</v>
@@ -7759,28 +7759,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M79">
-        <v>138.4478634</v>
+        <v>140.2458876</v>
       </c>
       <c r="N79">
-        <v>644.3076921555555</v>
+        <v>642.5096679555554</v>
       </c>
       <c r="O79">
-        <v>159.6286457273369</v>
+        <v>159.1831812830575</v>
       </c>
       <c r="P79">
-        <v>484.6790464282186</v>
+        <v>483.3264866724979</v>
       </c>
       <c r="Q79">
-        <v>675.4790464282187</v>
+        <v>674.1264866724979</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1320451828698315</v>
+        <v>0.1356893701359585</v>
       </c>
       <c r="T79">
-        <v>1.991805609003038</v>
+        <v>2.075966977735762</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.653792960993831</v>
+        <v>5.581308435852884</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06229911820121292</v>
+        <v>0.06219638060659205</v>
       </c>
       <c r="C80">
-        <v>808.3420259016757</v>
+        <v>777.5610335532538</v>
       </c>
       <c r="D80">
-        <v>3143.434025901676</v>
+        <v>3145.167033553254</v>
       </c>
       <c r="E80">
-        <v>1634.692</v>
+        <v>1667.206</v>
       </c>
       <c r="F80">
-        <v>2536.092</v>
+        <v>2568.606</v>
       </c>
       <c r="G80">
         <v>201</v>
@@ -7841,28 +7841,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M80">
-        <v>140.2458876</v>
+        <v>142.0439118</v>
       </c>
       <c r="N80">
-        <v>642.5096679555554</v>
+        <v>640.7116437555554</v>
       </c>
       <c r="O80">
-        <v>159.1831812830575</v>
+        <v>158.7377168387782</v>
       </c>
       <c r="P80">
-        <v>483.3264866724979</v>
+        <v>481.9739269167773</v>
       </c>
       <c r="Q80">
-        <v>674.1264866724979</v>
+        <v>672.7739269167773</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1356893701359585</v>
+        <v>0.1396806228560023</v>
       </c>
       <c r="T80">
-        <v>2.075966977735762</v>
+        <v>2.168143714919222</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.581308435852884</v>
+        <v>5.510658961981329</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.06219638060659205</v>
+        <v>0.06209364301197118</v>
       </c>
       <c r="C81">
-        <v>777.5610335532538</v>
+        <v>746.7819531089258</v>
       </c>
       <c r="D81">
-        <v>3145.167033553254</v>
+        <v>3146.901953108926</v>
       </c>
       <c r="E81">
-        <v>1667.206</v>
+        <v>1699.72</v>
       </c>
       <c r="F81">
-        <v>2568.606</v>
+        <v>2601.12</v>
       </c>
       <c r="G81">
         <v>201</v>
@@ -7923,28 +7923,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M81">
-        <v>142.0439118</v>
+        <v>143.841936</v>
       </c>
       <c r="N81">
-        <v>640.7116437555554</v>
+        <v>638.9136195555554</v>
       </c>
       <c r="O81">
-        <v>158.7377168387782</v>
+        <v>158.2922523944989</v>
       </c>
       <c r="P81">
-        <v>481.9739269167773</v>
+        <v>480.6213671610566</v>
       </c>
       <c r="Q81">
-        <v>672.7739269167773</v>
+        <v>671.4213671610567</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1396806228560023</v>
+        <v>0.1440710008480505</v>
       </c>
       <c r="T81">
-        <v>2.168143714919222</v>
+        <v>2.269538125821028</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.510658961981329</v>
+        <v>5.441775724956561</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.06209364301197118</v>
+        <v>0.06199090541735031</v>
       </c>
       <c r="C82">
-        <v>746.7819531089258</v>
+        <v>716.0047877343409</v>
       </c>
       <c r="D82">
-        <v>3146.901953108926</v>
+        <v>3148.638787734341</v>
       </c>
       <c r="E82">
-        <v>1699.72</v>
+        <v>1732.234</v>
       </c>
       <c r="F82">
-        <v>2601.12</v>
+        <v>2633.634</v>
       </c>
       <c r="G82">
         <v>201</v>
@@ -8005,28 +8005,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M82">
-        <v>143.841936</v>
+        <v>145.6399602</v>
       </c>
       <c r="N82">
-        <v>638.9136195555554</v>
+        <v>637.1155953555555</v>
       </c>
       <c r="O82">
-        <v>158.2922523944989</v>
+        <v>157.8467879502195</v>
       </c>
       <c r="P82">
-        <v>480.6213671610566</v>
+        <v>479.2688074053359</v>
       </c>
       <c r="Q82">
-        <v>671.4213671610567</v>
+        <v>670.068807405336</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1440710008480505</v>
+        <v>0.1489235238918932</v>
       </c>
       <c r="T82">
-        <v>2.269538125821028</v>
+        <v>2.381605632607234</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.441775724956561</v>
+        <v>5.374593308599073</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06199090541735031</v>
+        <v>0.06188816782272943</v>
       </c>
       <c r="C83">
-        <v>716.0047877343409</v>
+        <v>685.229540602139</v>
       </c>
       <c r="D83">
-        <v>3148.638787734341</v>
+        <v>3150.377540602139</v>
       </c>
       <c r="E83">
-        <v>1732.234</v>
+        <v>1764.748</v>
       </c>
       <c r="F83">
-        <v>2633.634</v>
+        <v>2666.148</v>
       </c>
       <c r="G83">
         <v>201</v>
@@ -8087,28 +8087,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M83">
-        <v>145.6399602</v>
+        <v>147.4379844</v>
       </c>
       <c r="N83">
-        <v>637.1155953555555</v>
+        <v>635.3175711555555</v>
       </c>
       <c r="O83">
-        <v>157.8467879502195</v>
+        <v>157.4013235059402</v>
       </c>
       <c r="P83">
-        <v>479.2688074053359</v>
+        <v>477.9162476496153</v>
       </c>
       <c r="Q83">
-        <v>670.068807405336</v>
+        <v>668.7162476496153</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1489235238918932</v>
+        <v>0.1543152161628296</v>
       </c>
       <c r="T83">
-        <v>2.381605632607234</v>
+        <v>2.506125084591908</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.374593308599073</v>
+        <v>5.3090494877625</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06188816782272943</v>
+        <v>0.06178543022810856</v>
       </c>
       <c r="C84">
-        <v>685.229540602139</v>
+        <v>654.4562148919726</v>
       </c>
       <c r="D84">
-        <v>3150.377540602139</v>
+        <v>3152.118214891973</v>
       </c>
       <c r="E84">
-        <v>1764.748</v>
+        <v>1797.262</v>
       </c>
       <c r="F84">
-        <v>2666.148</v>
+        <v>2698.662</v>
       </c>
       <c r="G84">
         <v>201</v>
@@ -8169,28 +8169,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M84">
-        <v>147.4379844</v>
+        <v>149.2360086</v>
       </c>
       <c r="N84">
-        <v>635.3175711555555</v>
+        <v>633.5195469555555</v>
       </c>
       <c r="O84">
-        <v>157.4013235059402</v>
+        <v>156.9558590616608</v>
       </c>
       <c r="P84">
-        <v>477.9162476496153</v>
+        <v>476.5636878938947</v>
       </c>
       <c r="Q84">
-        <v>668.7162476496153</v>
+        <v>667.3636878938946</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1543152161628296</v>
+        <v>0.1603412251715232</v>
       </c>
       <c r="T84">
-        <v>2.506125084591908</v>
+        <v>2.645293883868896</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.3090494877625</v>
+        <v>5.245085036102711</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06178543022810856</v>
+        <v>0.06168269263348769</v>
       </c>
       <c r="C85">
-        <v>654.4562148919726</v>
+        <v>623.6848137905249</v>
       </c>
       <c r="D85">
-        <v>3152.118214891973</v>
+        <v>3153.860813790525</v>
       </c>
       <c r="E85">
-        <v>1797.262</v>
+        <v>1829.776</v>
       </c>
       <c r="F85">
-        <v>2698.662</v>
+        <v>2731.176</v>
       </c>
       <c r="G85">
         <v>201</v>
@@ -8251,28 +8251,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M85">
-        <v>149.2360086</v>
+        <v>151.0340328</v>
       </c>
       <c r="N85">
-        <v>633.5195469555555</v>
+        <v>631.7215227555555</v>
       </c>
       <c r="O85">
-        <v>156.9558590616608</v>
+        <v>156.5103946173815</v>
       </c>
       <c r="P85">
-        <v>476.5636878938947</v>
+        <v>475.211128138174</v>
       </c>
       <c r="Q85">
-        <v>667.3636878938946</v>
+        <v>666.0111281381739</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1603412251715232</v>
+        <v>0.1671204853063035</v>
       </c>
       <c r="T85">
-        <v>2.645293883868896</v>
+        <v>2.801858783055509</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.245085036102711</v>
+        <v>5.182643547577678</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.06168269263348769</v>
+        <v>0.06157995503886682</v>
       </c>
       <c r="C86">
-        <v>623.6848137905254</v>
+        <v>592.9153404915323</v>
       </c>
       <c r="D86">
-        <v>3153.860813790525</v>
+        <v>3155.605340491532</v>
       </c>
       <c r="E86">
-        <v>1829.776</v>
+        <v>1862.29</v>
       </c>
       <c r="F86">
-        <v>2731.176</v>
+        <v>2763.69</v>
       </c>
       <c r="G86">
         <v>201</v>
@@ -8333,28 +8333,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M86">
-        <v>151.0340328</v>
+        <v>152.832057</v>
       </c>
       <c r="N86">
-        <v>631.7215227555555</v>
+        <v>629.9234985555554</v>
       </c>
       <c r="O86">
-        <v>156.5103946173815</v>
+        <v>156.0649301731021</v>
       </c>
       <c r="P86">
-        <v>475.211128138174</v>
+        <v>473.8585683824533</v>
       </c>
       <c r="Q86">
-        <v>666.0111281381739</v>
+        <v>664.6585683824533</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1671204853063034</v>
+        <v>0.1748036467923878</v>
       </c>
       <c r="T86">
-        <v>2.801858783055506</v>
+        <v>2.979299002133667</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.182643547577679</v>
+        <v>5.121671270547352</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.06157995503886682</v>
+        <v>0.06147721744424595</v>
       </c>
       <c r="C87">
-        <v>592.9153404915323</v>
+        <v>562.1477981957964</v>
       </c>
       <c r="D87">
-        <v>3155.605340491532</v>
+        <v>3157.351798195797</v>
       </c>
       <c r="E87">
-        <v>1862.29</v>
+        <v>1894.804</v>
       </c>
       <c r="F87">
-        <v>2763.69</v>
+        <v>2796.204</v>
       </c>
       <c r="G87">
         <v>201</v>
@@ -8415,28 +8415,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M87">
-        <v>152.832057</v>
+        <v>154.6300812</v>
       </c>
       <c r="N87">
-        <v>629.9234985555554</v>
+        <v>628.1254743555555</v>
       </c>
       <c r="O87">
-        <v>156.0649301731021</v>
+        <v>155.6194657288228</v>
       </c>
       <c r="P87">
-        <v>473.8585683824533</v>
+        <v>472.5060086267327</v>
       </c>
       <c r="Q87">
-        <v>664.6585683824533</v>
+        <v>663.3060086267327</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1748036467923878</v>
+        <v>0.1835844027764842</v>
       </c>
       <c r="T87">
-        <v>2.979299002133667</v>
+        <v>3.182087823937279</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.121671270547352</v>
+        <v>5.062116953447966</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.06147721744424595</v>
+        <v>0.06137447984962507</v>
       </c>
       <c r="C88">
-        <v>562.1477981957964</v>
+        <v>531.3821901112151</v>
       </c>
       <c r="D88">
-        <v>3157.351798195797</v>
+        <v>3159.100190111215</v>
       </c>
       <c r="E88">
-        <v>1894.804</v>
+        <v>1927.318</v>
       </c>
       <c r="F88">
-        <v>2796.204</v>
+        <v>2828.718</v>
       </c>
       <c r="G88">
         <v>201</v>
@@ -8497,28 +8497,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M88">
-        <v>154.6300812</v>
+        <v>156.4281054</v>
       </c>
       <c r="N88">
-        <v>628.1254743555555</v>
+        <v>626.3274501555554</v>
       </c>
       <c r="O88">
-        <v>155.6194657288228</v>
+        <v>155.1740012845435</v>
       </c>
       <c r="P88">
-        <v>472.5060086267327</v>
+        <v>471.153448871012</v>
       </c>
       <c r="Q88">
-        <v>663.3060086267327</v>
+        <v>661.9534488710119</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1835844027764842</v>
+        <v>0.1937160442965953</v>
       </c>
       <c r="T88">
-        <v>3.182087823937279</v>
+        <v>3.416074926018368</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.062116953447966</v>
+        <v>5.003931701109483</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.06137447984962507</v>
+        <v>0.06127174225500421</v>
       </c>
       <c r="C89">
-        <v>531.3821901112151</v>
+        <v>500.6185194527889</v>
       </c>
       <c r="D89">
-        <v>3159.100190111215</v>
+        <v>3160.850519452789</v>
       </c>
       <c r="E89">
-        <v>1927.318</v>
+        <v>1959.832</v>
       </c>
       <c r="F89">
-        <v>2828.718</v>
+        <v>2861.232</v>
       </c>
       <c r="G89">
         <v>201</v>
@@ -8579,28 +8579,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M89">
-        <v>156.4281054</v>
+        <v>158.2261296</v>
       </c>
       <c r="N89">
-        <v>626.3274501555554</v>
+        <v>624.5294259555554</v>
       </c>
       <c r="O89">
-        <v>155.1740012845435</v>
+        <v>154.7285368402641</v>
       </c>
       <c r="P89">
-        <v>471.153448871012</v>
+        <v>469.8008891152913</v>
       </c>
       <c r="Q89">
-        <v>661.9534488710119</v>
+        <v>660.6008891152912</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1937160442965953</v>
+        <v>0.2055362927367251</v>
       </c>
       <c r="T89">
-        <v>3.416074926018368</v>
+        <v>3.689059878446307</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.003931701109483</v>
+        <v>4.947068840869601</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.06127174225500421</v>
+        <v>0.06116900466038333</v>
       </c>
       <c r="C90">
-        <v>500.6185194527889</v>
+        <v>469.8567894426537</v>
       </c>
       <c r="D90">
-        <v>3160.850519452789</v>
+        <v>3162.602789442654</v>
       </c>
       <c r="E90">
-        <v>1959.832</v>
+        <v>1992.346</v>
       </c>
       <c r="F90">
-        <v>2861.232</v>
+        <v>2893.746</v>
       </c>
       <c r="G90">
         <v>201</v>
@@ -8661,28 +8661,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M90">
-        <v>158.2261296</v>
+        <v>160.0241538</v>
       </c>
       <c r="N90">
-        <v>624.5294259555554</v>
+        <v>622.7314017555555</v>
       </c>
       <c r="O90">
-        <v>154.7285368402641</v>
+        <v>154.2830723959848</v>
       </c>
       <c r="P90">
-        <v>469.8008891152913</v>
+        <v>468.4483293595706</v>
       </c>
       <c r="Q90">
-        <v>660.6008891152912</v>
+        <v>659.2483293595706</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2055362927367251</v>
+        <v>0.2195056772568784</v>
       </c>
       <c r="T90">
-        <v>3.689059878446307</v>
+        <v>4.011678458588416</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.947068840869601</v>
+        <v>4.891483797713764</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.06116900466038333</v>
+        <v>0.06106626706576246</v>
       </c>
       <c r="C91">
-        <v>469.8567894426537</v>
+        <v>439.0970033100898</v>
       </c>
       <c r="D91">
-        <v>3162.602789442654</v>
+        <v>3164.35700331009</v>
       </c>
       <c r="E91">
-        <v>1992.346</v>
+        <v>2024.86</v>
       </c>
       <c r="F91">
-        <v>2893.746</v>
+        <v>2926.26</v>
       </c>
       <c r="G91">
         <v>201</v>
@@ -8743,28 +8743,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M91">
-        <v>160.0241538</v>
+        <v>161.822178</v>
       </c>
       <c r="N91">
-        <v>622.7314017555555</v>
+        <v>620.9333775555555</v>
       </c>
       <c r="O91">
-        <v>154.2830723959848</v>
+        <v>153.8376079517055</v>
       </c>
       <c r="P91">
-        <v>468.4483293595706</v>
+        <v>467.09576960385</v>
       </c>
       <c r="Q91">
-        <v>659.2483293595706</v>
+        <v>657.89576960385</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2195056772568784</v>
+        <v>0.2362689386810624</v>
       </c>
       <c r="T91">
-        <v>4.011678458588416</v>
+        <v>4.398820754758948</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.891483797713764</v>
+        <v>4.837133977739167</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.06106626706576246</v>
+        <v>0.06096352947114159</v>
       </c>
       <c r="C92">
-        <v>439.0970033100898</v>
+        <v>408.3391642915485</v>
       </c>
       <c r="D92">
-        <v>3164.35700331009</v>
+        <v>3166.113164291549</v>
       </c>
       <c r="E92">
-        <v>2024.86</v>
+        <v>2057.374</v>
       </c>
       <c r="F92">
-        <v>2926.26</v>
+        <v>2958.774</v>
       </c>
       <c r="G92">
         <v>201</v>
@@ -8825,28 +8825,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M92">
-        <v>161.822178</v>
+        <v>163.6202022</v>
       </c>
       <c r="N92">
-        <v>620.9333775555555</v>
+        <v>619.1353533555555</v>
       </c>
       <c r="O92">
-        <v>153.8376079517055</v>
+        <v>153.3921435074261</v>
       </c>
       <c r="P92">
-        <v>467.09576960385</v>
+        <v>465.7432098481294</v>
       </c>
       <c r="Q92">
-        <v>657.89576960385</v>
+        <v>656.5432098481294</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2362689386810624</v>
+        <v>0.2567573693106207</v>
       </c>
       <c r="T92">
-        <v>4.398820754758948</v>
+        <v>4.871994672300708</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.837133977739167</v>
+        <v>4.783978659302472</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.06096352947114159</v>
+        <v>0.06086079187652071</v>
       </c>
       <c r="C93">
-        <v>408.3391642915485</v>
+        <v>377.58327563067</v>
       </c>
       <c r="D93">
-        <v>3166.113164291549</v>
+        <v>3167.87127563067</v>
       </c>
       <c r="E93">
-        <v>2057.374</v>
+        <v>2089.888</v>
       </c>
       <c r="F93">
-        <v>2958.774</v>
+        <v>2991.288</v>
       </c>
       <c r="G93">
         <v>201</v>
@@ -8907,28 +8907,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M93">
-        <v>163.6202022</v>
+        <v>165.4182264</v>
       </c>
       <c r="N93">
-        <v>619.1353533555555</v>
+        <v>617.3373291555555</v>
       </c>
       <c r="O93">
-        <v>153.3921435074261</v>
+        <v>152.9466790631468</v>
       </c>
       <c r="P93">
-        <v>465.7432098481294</v>
+        <v>464.3906500924087</v>
       </c>
       <c r="Q93">
-        <v>656.5432098481294</v>
+        <v>655.1906500924088</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2567573693106207</v>
+        <v>0.2823679075975685</v>
       </c>
       <c r="T93">
-        <v>4.871994672300708</v>
+        <v>5.463462069227909</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.783978659302472</v>
+        <v>4.731978891266576</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.06086079187652071</v>
+        <v>0.06075805428189984</v>
       </c>
       <c r="C94">
-        <v>377.58327563067</v>
+        <v>346.8293405783024</v>
       </c>
       <c r="D94">
-        <v>3167.87127563067</v>
+        <v>3169.631340578303</v>
       </c>
       <c r="E94">
-        <v>2089.888</v>
+        <v>2122.402</v>
       </c>
       <c r="F94">
-        <v>2991.288</v>
+        <v>3023.802</v>
       </c>
       <c r="G94">
         <v>201</v>
@@ -8989,28 +8989,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M94">
-        <v>165.4182264</v>
+        <v>167.2162506</v>
       </c>
       <c r="N94">
-        <v>617.3373291555555</v>
+        <v>615.5393049555555</v>
       </c>
       <c r="O94">
-        <v>152.9466790631468</v>
+        <v>152.5012146188675</v>
       </c>
       <c r="P94">
-        <v>464.3906500924087</v>
+        <v>463.038090336688</v>
       </c>
       <c r="Q94">
-        <v>655.1906500924088</v>
+        <v>653.8380903366881</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2823679075975685</v>
+        <v>0.3152957425379299</v>
       </c>
       <c r="T94">
-        <v>5.463462069227909</v>
+        <v>6.223920150991453</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.731978891266576</v>
+        <v>4.681097397812096</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.06075805428189984</v>
+        <v>0.06065531668727897</v>
       </c>
       <c r="C95">
-        <v>346.8293405783024</v>
+        <v>316.0773623925211</v>
       </c>
       <c r="D95">
-        <v>3169.631340578303</v>
+        <v>3171.393362392521</v>
       </c>
       <c r="E95">
-        <v>2122.402</v>
+        <v>2154.916</v>
       </c>
       <c r="F95">
-        <v>3023.802</v>
+        <v>3056.316</v>
       </c>
       <c r="G95">
         <v>201</v>
@@ -9071,28 +9071,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M95">
-        <v>167.2162506</v>
+        <v>169.0142748</v>
       </c>
       <c r="N95">
-        <v>615.5393049555555</v>
+        <v>613.7412807555554</v>
       </c>
       <c r="O95">
-        <v>152.5012146188675</v>
+        <v>152.0557501745881</v>
       </c>
       <c r="P95">
-        <v>463.038090336688</v>
+        <v>461.6855305809673</v>
       </c>
       <c r="Q95">
-        <v>653.8380903366881</v>
+        <v>652.4855305809674</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3152957425379299</v>
+        <v>0.3591995224584119</v>
       </c>
       <c r="T95">
-        <v>6.223920150991453</v>
+        <v>7.237864260009513</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.681097397812096</v>
+        <v>4.631298489324733</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06065531668727897</v>
+        <v>0.0605525790926581</v>
       </c>
       <c r="C96">
-        <v>316.0773623925211</v>
+        <v>285.3273443386529</v>
       </c>
       <c r="D96">
-        <v>3171.393362392521</v>
+        <v>3173.157344338653</v>
       </c>
       <c r="E96">
-        <v>2154.916</v>
+        <v>2187.43</v>
       </c>
       <c r="F96">
-        <v>3056.316</v>
+        <v>3088.83</v>
       </c>
       <c r="G96">
         <v>201</v>
@@ -9153,28 +9153,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M96">
-        <v>169.0142748</v>
+        <v>170.812299</v>
       </c>
       <c r="N96">
-        <v>613.7412807555554</v>
+        <v>611.9432565555554</v>
       </c>
       <c r="O96">
-        <v>152.0557501745881</v>
+        <v>151.6102857303088</v>
       </c>
       <c r="P96">
-        <v>461.6855305809673</v>
+        <v>460.3329708252467</v>
       </c>
       <c r="Q96">
-        <v>652.4855305809674</v>
+        <v>651.1329708252467</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3591995224584119</v>
+        <v>0.4206648143470867</v>
       </c>
       <c r="T96">
-        <v>7.237864260009513</v>
+        <v>8.657386012634797</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.631298489324733</v>
+        <v>4.582547978910789</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.0605525790926581</v>
+        <v>0.06044984149803722</v>
       </c>
       <c r="C97">
-        <v>285.3273443386529</v>
+        <v>254.5792896892926</v>
       </c>
       <c r="D97">
-        <v>3173.157344338653</v>
+        <v>3174.923289689293</v>
       </c>
       <c r="E97">
-        <v>2187.43</v>
+        <v>2219.944</v>
       </c>
       <c r="F97">
-        <v>3088.83</v>
+        <v>3121.344000000001</v>
       </c>
       <c r="G97">
         <v>201</v>
@@ -9235,28 +9235,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M97">
-        <v>170.812299</v>
+        <v>172.6103232</v>
       </c>
       <c r="N97">
-        <v>611.9432565555554</v>
+        <v>610.1452323555554</v>
       </c>
       <c r="O97">
-        <v>151.6102857303088</v>
+        <v>151.1648212860294</v>
       </c>
       <c r="P97">
-        <v>460.3329708252467</v>
+        <v>458.980411069526</v>
       </c>
       <c r="Q97">
-        <v>651.1329708252467</v>
+        <v>649.7804110695261</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4206648143470867</v>
+        <v>0.5128627521800989</v>
       </c>
       <c r="T97">
-        <v>8.657386012634797</v>
+        <v>10.78666864157272</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.582547978910789</v>
+        <v>4.534813104130468</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.06044984149803723</v>
+        <v>0.06217130482775464</v>
       </c>
       <c r="C98">
-        <v>254.5792896892931</v>
+        <v>192.7323092428537</v>
       </c>
       <c r="D98">
-        <v>3174.923289689293</v>
+        <v>3145.590309242854</v>
       </c>
       <c r="E98">
-        <v>2219.944</v>
+        <v>2252.458</v>
       </c>
       <c r="F98">
-        <v>3121.344</v>
+        <v>3153.858</v>
       </c>
       <c r="G98">
         <v>201</v>
@@ -9317,45 +9317,45 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M98">
-        <v>172.6103232</v>
+        <v>182.2929924</v>
       </c>
       <c r="N98">
-        <v>610.1452323555554</v>
+        <v>600.4625631555555</v>
       </c>
       <c r="O98">
-        <v>151.1648212860294</v>
+        <v>148.7659187271436</v>
       </c>
       <c r="P98">
-        <v>458.980411069526</v>
+        <v>451.6966444284119</v>
       </c>
       <c r="Q98">
-        <v>649.7804110695261</v>
+        <v>642.4966444284119</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5128627521800977</v>
+        <v>0.666525981901784</v>
       </c>
       <c r="T98">
-        <v>10.7866686415727</v>
+        <v>14.33547302313589</v>
       </c>
       <c r="U98">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V98">
         <v>0.2477521961491617</v>
       </c>
       <c r="W98">
-        <v>0.04159930355295136</v>
+        <v>0.04347992306257845</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y98">
-        <v>4.534813104130468</v>
+        <v>4.293942105234515</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.06217130482775464</v>
+        <v>0.06208737342823004</v>
       </c>
       <c r="C99">
-        <v>192.7323092428537</v>
+        <v>161.6358889144099</v>
       </c>
       <c r="D99">
-        <v>3145.590309242854</v>
+        <v>3147.00788891441</v>
       </c>
       <c r="E99">
-        <v>2252.458</v>
+        <v>2284.972</v>
       </c>
       <c r="F99">
-        <v>3153.858</v>
+        <v>3186.372</v>
       </c>
       <c r="G99">
         <v>201</v>
@@ -9399,28 +9399,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M99">
-        <v>182.2929924</v>
+        <v>184.1723016</v>
       </c>
       <c r="N99">
-        <v>600.4625631555555</v>
+        <v>598.5832539555555</v>
       </c>
       <c r="O99">
-        <v>148.7659187271436</v>
+        <v>148.3003157456003</v>
       </c>
       <c r="P99">
-        <v>451.6966444284119</v>
+        <v>450.2829382099552</v>
       </c>
       <c r="Q99">
-        <v>642.4966444284119</v>
+        <v>641.0829382099553</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.666525981901784</v>
+        <v>0.9738524413451567</v>
       </c>
       <c r="T99">
-        <v>14.33547302313589</v>
+        <v>21.43308178626228</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.293942105234515</v>
+        <v>4.250126369466816</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.06208737342823004</v>
+        <v>0.06200344202870544</v>
       </c>
       <c r="C100">
-        <v>161.6358889144099</v>
+        <v>130.5407468440626</v>
       </c>
       <c r="D100">
-        <v>3147.00788891441</v>
+        <v>3148.426746844063</v>
       </c>
       <c r="E100">
-        <v>2284.972</v>
+        <v>2317.486</v>
       </c>
       <c r="F100">
-        <v>3186.372</v>
+        <v>3218.886</v>
       </c>
       <c r="G100">
         <v>201</v>
@@ -9481,28 +9481,28 @@
         <v>782.7555555555555</v>
       </c>
       <c r="M100">
-        <v>184.1723016</v>
+        <v>186.0516108</v>
       </c>
       <c r="N100">
-        <v>598.5832539555555</v>
+        <v>596.7039447555554</v>
       </c>
       <c r="O100">
-        <v>148.3003157456003</v>
+        <v>147.8347127640569</v>
       </c>
       <c r="P100">
-        <v>450.2829382099552</v>
+        <v>448.8692319914985</v>
       </c>
       <c r="Q100">
-        <v>641.0829382099553</v>
+        <v>639.6692319914985</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.9738524413451567</v>
+        <v>1.895831819675275</v>
       </c>
       <c r="T100">
-        <v>21.43308178626228</v>
+        <v>42.72590807564146</v>
       </c>
       <c r="U100">
         <v>0.0578</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.250126369466816</v>
+        <v>4.207195800078262</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.06200344202870544</v>
-      </c>
-      <c r="C101">
-        <v>130.5407468440626</v>
-      </c>
-      <c r="D101">
-        <v>3148.426746844063</v>
-      </c>
-      <c r="E101">
-        <v>2317.486</v>
-      </c>
-      <c r="F101">
-        <v>3218.886</v>
-      </c>
-      <c r="G101">
-        <v>201</v>
-      </c>
-      <c r="H101">
-        <v>2350</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>973.5555555555555</v>
-      </c>
-      <c r="K101">
-        <v>190.8</v>
-      </c>
-      <c r="L101">
-        <v>782.7555555555555</v>
-      </c>
-      <c r="M101">
-        <v>186.0516108</v>
-      </c>
-      <c r="N101">
-        <v>596.7039447555554</v>
-      </c>
-      <c r="O101">
-        <v>147.8347127640569</v>
-      </c>
-      <c r="P101">
-        <v>448.8692319914985</v>
-      </c>
-      <c r="Q101">
-        <v>639.6692319914985</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.895831819675275</v>
-      </c>
-      <c r="T101">
-        <v>42.72590807564146</v>
-      </c>
-      <c r="U101">
-        <v>0.0578</v>
-      </c>
-      <c r="V101">
-        <v>0.2477521961491617</v>
-      </c>
-      <c r="W101">
-        <v>0.04347992306257845</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.207195800078262</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
